--- a/Temel_Analiz_Omurga.xlsx
+++ b/Temel_Analiz_Omurga.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Tetik Bölgesi</t>
+          <t>Temel Skor</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
@@ -552,7 +552,9 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>47</v>
+      </c>
       <c r="Q2" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -604,7 +606,9 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>39</v>
+      </c>
       <c r="Q3" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -656,10 +660,12 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>30</v>
+      </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>✅ Temiz</t>
+          <t>🚨 RİSKLİ (%46.4)</t>
         </is>
       </c>
       <c r="R4" t="inlineStr"/>
@@ -712,7 +718,9 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>40</v>
+      </c>
       <c r="Q5" t="inlineStr">
         <is>
           <t>✅ Finans / Muaf</t>
@@ -764,7 +772,9 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>49</v>
+      </c>
       <c r="Q6" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -816,7 +826,9 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>57</v>
+      </c>
       <c r="Q7" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -868,7 +880,9 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
+      <c r="P8" t="n">
+        <v>55</v>
+      </c>
       <c r="Q8" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -920,7 +934,9 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
+      <c r="P9" t="n">
+        <v>34</v>
+      </c>
       <c r="Q9" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -972,7 +988,9 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
+      <c r="P10" t="n">
+        <v>64</v>
+      </c>
       <c r="Q10" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -1028,7 +1046,9 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
+      <c r="P11" t="n">
+        <v>55</v>
+      </c>
       <c r="Q11" t="inlineStr">
         <is>
           <t>✅ Finans / Muaf</t>
@@ -1080,7 +1100,9 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
+      <c r="P12" t="n">
+        <v>49</v>
+      </c>
       <c r="Q12" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -1136,7 +1158,9 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
+      <c r="P13" t="n">
+        <v>70</v>
+      </c>
       <c r="Q13" t="inlineStr">
         <is>
           <t>✅ Finans / Muaf</t>
@@ -1192,7 +1216,9 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
+      <c r="P14" t="n">
+        <v>100</v>
+      </c>
       <c r="Q14" t="inlineStr">
         <is>
           <t>✅ Finans / Muaf</t>
@@ -1244,7 +1270,9 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
+      <c r="P15" t="n">
+        <v>30</v>
+      </c>
       <c r="Q15" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -1296,7 +1324,9 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
+      <c r="P16" t="n">
+        <v>57</v>
+      </c>
       <c r="Q16" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -1348,7 +1378,9 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
+      <c r="P17" t="n">
+        <v>77</v>
+      </c>
       <c r="Q17" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -1400,7 +1432,9 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
+      <c r="P18" t="n">
+        <v>60</v>
+      </c>
       <c r="Q18" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -1452,7 +1486,9 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
+      <c r="P19" t="n">
+        <v>40</v>
+      </c>
       <c r="Q19" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -1504,7 +1540,9 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
+      <c r="P20" t="n">
+        <v>57</v>
+      </c>
       <c r="Q20" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -1556,10 +1594,12 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
+      <c r="P21" t="n">
+        <v>13</v>
+      </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>✅ Temiz</t>
+          <t>🚨 RİSKLİ (%24.4)</t>
         </is>
       </c>
       <c r="R21" t="inlineStr"/>
@@ -1608,7 +1648,9 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
+      <c r="P22" t="n">
+        <v>56</v>
+      </c>
       <c r="Q22" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -1660,7 +1702,9 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
+      <c r="P23" t="n">
+        <v>56</v>
+      </c>
       <c r="Q23" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -1712,7 +1756,9 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
+      <c r="P24" t="n">
+        <v>36</v>
+      </c>
       <c r="Q24" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -1764,7 +1810,9 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
+      <c r="P25" t="n">
+        <v>40</v>
+      </c>
       <c r="Q25" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -1816,7 +1864,9 @@
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
+      <c r="P26" t="n">
+        <v>71</v>
+      </c>
       <c r="Q26" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -1868,7 +1918,9 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
+      <c r="P27" t="n">
+        <v>48</v>
+      </c>
       <c r="Q27" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -1920,10 +1972,12 @@
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
+      <c r="P28" t="n">
+        <v>25</v>
+      </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>✅ Temiz</t>
+          <t>⚠️ Dikkat (%5.1)</t>
         </is>
       </c>
       <c r="R28" t="inlineStr"/>
@@ -1972,10 +2026,12 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
+      <c r="P29" t="n">
+        <v>34</v>
+      </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>✅ Temiz</t>
+          <t>🚨 RİSKLİ (%17.9)</t>
         </is>
       </c>
       <c r="R29" t="inlineStr"/>
@@ -2024,10 +2080,12 @@
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
+      <c r="P30" t="n">
+        <v>22</v>
+      </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>✅ Temiz</t>
+          <t>🚨 RİSKLİ (%17.5)</t>
         </is>
       </c>
       <c r="R30" t="inlineStr"/>
@@ -2076,10 +2134,12 @@
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
+      <c r="P31" t="n">
+        <v>30</v>
+      </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>✅ Temiz</t>
+          <t>⚠️ Dikkat (%14.9)</t>
         </is>
       </c>
       <c r="R31" t="inlineStr"/>
@@ -2128,7 +2188,9 @@
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
+      <c r="P32" t="n">
+        <v>38</v>
+      </c>
       <c r="Q32" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -2180,7 +2242,9 @@
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
+      <c r="P33" t="n">
+        <v>31</v>
+      </c>
       <c r="Q33" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -2236,7 +2300,9 @@
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
       <c r="Q34" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -2288,7 +2354,9 @@
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
+      <c r="P35" t="n">
+        <v>65</v>
+      </c>
       <c r="Q35" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -2340,7 +2408,9 @@
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
+      <c r="P36" t="n">
+        <v>36</v>
+      </c>
       <c r="Q36" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -2392,7 +2462,9 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
+      <c r="P37" t="n">
+        <v>55</v>
+      </c>
       <c r="Q37" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -2444,10 +2516,12 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
+      <c r="P38" t="n">
+        <v>14</v>
+      </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>✅ Temiz</t>
+          <t>⚠️ Dikkat (%13.7)</t>
         </is>
       </c>
       <c r="R38" t="inlineStr"/>
@@ -2496,7 +2570,9 @@
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
+      <c r="P39" t="n">
+        <v>65</v>
+      </c>
       <c r="Q39" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -2548,10 +2624,12 @@
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
+      <c r="P40" t="n">
+        <v>23</v>
+      </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>✅ Temiz</t>
+          <t>⚠️ Dikkat (%5.9)</t>
         </is>
       </c>
       <c r="R40" t="inlineStr"/>
@@ -2600,7 +2678,9 @@
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
+      <c r="P41" t="n">
+        <v>58</v>
+      </c>
       <c r="Q41" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -2652,7 +2732,9 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
+      <c r="P42" t="n">
+        <v>51</v>
+      </c>
       <c r="Q42" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -2704,10 +2786,12 @@
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
+      <c r="P43" t="n">
+        <v>18</v>
+      </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>✅ Temiz</t>
+          <t>🚨 RİSKLİ (%50.3)</t>
         </is>
       </c>
       <c r="R43" t="inlineStr"/>
@@ -2756,7 +2840,9 @@
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
+      <c r="P44" t="n">
+        <v>60</v>
+      </c>
       <c r="Q44" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -2812,7 +2898,9 @@
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
+      <c r="P45" t="n">
+        <v>70</v>
+      </c>
       <c r="Q45" t="inlineStr">
         <is>
           <t>✅ Finans / Muaf</t>
@@ -2864,10 +2952,12 @@
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
+      <c r="P46" t="n">
+        <v>24</v>
+      </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>✅ Temiz</t>
+          <t>🚨 RİSKLİ (%51.8)</t>
         </is>
       </c>
       <c r="R46" t="inlineStr"/>
@@ -2916,7 +3006,9 @@
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
+      <c r="P47" t="n">
+        <v>60</v>
+      </c>
       <c r="Q47" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -2968,7 +3060,9 @@
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
+      <c r="P48" t="n">
+        <v>77</v>
+      </c>
       <c r="Q48" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -3020,7 +3114,9 @@
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
+      <c r="P49" t="n">
+        <v>73</v>
+      </c>
       <c r="Q49" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -3072,7 +3168,9 @@
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
+      <c r="P50" t="n">
+        <v>61</v>
+      </c>
       <c r="Q50" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -3128,7 +3226,9 @@
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
+      <c r="P51" t="n">
+        <v>25</v>
+      </c>
       <c r="Q51" t="inlineStr">
         <is>
           <t>✅ Finans / Muaf</t>
@@ -3180,7 +3280,9 @@
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
+      <c r="P52" t="n">
+        <v>23</v>
+      </c>
       <c r="Q52" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -3236,7 +3338,9 @@
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
+      <c r="P53" t="n">
+        <v>40</v>
+      </c>
       <c r="Q53" t="inlineStr">
         <is>
           <t>✅ Finans / Muaf</t>
@@ -3288,7 +3392,9 @@
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
+      <c r="P54" t="n">
+        <v>68</v>
+      </c>
       <c r="Q54" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -3344,7 +3450,9 @@
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
+      <c r="P55" t="n">
+        <v>70</v>
+      </c>
       <c r="Q55" t="inlineStr">
         <is>
           <t>✅ Finans / Muaf</t>
@@ -3396,7 +3504,9 @@
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
+      <c r="P56" t="n">
+        <v>32</v>
+      </c>
       <c r="Q56" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -3448,7 +3558,9 @@
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
+      <c r="P57" t="n">
+        <v>43</v>
+      </c>
       <c r="Q57" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -3500,7 +3612,9 @@
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
+      <c r="P58" t="n">
+        <v>53</v>
+      </c>
       <c r="Q58" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -3552,10 +3666,12 @@
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
+      <c r="P59" t="n">
+        <v>9</v>
+      </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>✅ Temiz</t>
+          <t>🚨 RİSKLİ (%45.4)</t>
         </is>
       </c>
       <c r="R59" t="inlineStr"/>
@@ -3604,7 +3720,9 @@
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
+      <c r="P60" t="n">
+        <v>27</v>
+      </c>
       <c r="Q60" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -3656,7 +3774,9 @@
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
+      <c r="P61" t="n">
+        <v>62</v>
+      </c>
       <c r="Q61" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -3708,7 +3828,9 @@
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
+      <c r="P62" t="n">
+        <v>71</v>
+      </c>
       <c r="Q62" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -3760,7 +3882,9 @@
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
+      <c r="P63" t="n">
+        <v>55</v>
+      </c>
       <c r="Q63" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -3812,7 +3936,9 @@
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
+      <c r="P64" t="n">
+        <v>45</v>
+      </c>
       <c r="Q64" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -3864,10 +3990,12 @@
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
+      <c r="P65" t="n">
+        <v>34</v>
+      </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>✅ Temiz</t>
+          <t>🚨 RİSKLİ (%16.2)</t>
         </is>
       </c>
       <c r="R65" t="inlineStr"/>
@@ -3916,7 +4044,9 @@
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
+      <c r="P66" t="n">
+        <v>46</v>
+      </c>
       <c r="Q66" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -3968,10 +4098,12 @@
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
+      <c r="P67" t="n">
+        <v>13</v>
+      </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>✅ Temiz</t>
+          <t>⚠️ Dikkat (%6.0)</t>
         </is>
       </c>
       <c r="R67" t="inlineStr"/>
@@ -4020,7 +4152,9 @@
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr"/>
+      <c r="P68" t="n">
+        <v>11</v>
+      </c>
       <c r="Q68" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -4072,7 +4206,9 @@
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
+      <c r="P69" t="n">
+        <v>61</v>
+      </c>
       <c r="Q69" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -4124,10 +4260,12 @@
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr"/>
+      <c r="P70" t="n">
+        <v>24</v>
+      </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>✅ Temiz</t>
+          <t>🚨 RİSKLİ (%95.7)</t>
         </is>
       </c>
       <c r="R70" t="inlineStr"/>
@@ -4176,7 +4314,9 @@
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
-      <c r="P71" t="inlineStr"/>
+      <c r="P71" t="n">
+        <v>34</v>
+      </c>
       <c r="Q71" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -4228,7 +4368,9 @@
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr"/>
+      <c r="P72" t="n">
+        <v>14</v>
+      </c>
       <c r="Q72" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -4280,7 +4422,9 @@
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr"/>
+      <c r="P73" t="n">
+        <v>63</v>
+      </c>
       <c r="Q73" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -4332,7 +4476,9 @@
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr"/>
+      <c r="P74" t="n">
+        <v>61</v>
+      </c>
       <c r="Q74" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -4384,7 +4530,9 @@
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
-      <c r="P75" t="inlineStr"/>
+      <c r="P75" t="n">
+        <v>38</v>
+      </c>
       <c r="Q75" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -4436,7 +4584,9 @@
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr"/>
+      <c r="P76" t="n">
+        <v>23</v>
+      </c>
       <c r="Q76" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -4488,7 +4638,9 @@
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
+      <c r="P77" t="n">
+        <v>45</v>
+      </c>
       <c r="Q77" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -4540,7 +4692,9 @@
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
-      <c r="P78" t="inlineStr"/>
+      <c r="P78" t="n">
+        <v>38</v>
+      </c>
       <c r="Q78" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -4592,7 +4746,9 @@
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
-      <c r="P79" t="inlineStr"/>
+      <c r="P79" t="n">
+        <v>33</v>
+      </c>
       <c r="Q79" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -4644,7 +4800,9 @@
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
+      <c r="P80" t="n">
+        <v>57</v>
+      </c>
       <c r="Q80" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -4696,10 +4854,12 @@
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
-      <c r="P81" t="inlineStr"/>
+      <c r="P81" t="n">
+        <v>11</v>
+      </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>✅ Temiz</t>
+          <t>⚠️ Dikkat (%7.0)</t>
         </is>
       </c>
       <c r="R81" t="inlineStr"/>
@@ -4748,10 +4908,12 @@
       <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr"/>
+      <c r="P82" t="n">
+        <v>26</v>
+      </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>✅ Temiz</t>
+          <t>⚠️ Dikkat (%6.3)</t>
         </is>
       </c>
       <c r="R82" t="inlineStr"/>
@@ -4800,10 +4962,12 @@
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
-      <c r="P83" t="inlineStr"/>
+      <c r="P83" t="n">
+        <v>55</v>
+      </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>✅ Temiz</t>
+          <t>🚨 RİSKLİ (%50.1)</t>
         </is>
       </c>
       <c r="R83" t="inlineStr"/>
@@ -4852,7 +5016,9 @@
       <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
-      <c r="P84" t="inlineStr"/>
+      <c r="P84" t="n">
+        <v>46</v>
+      </c>
       <c r="Q84" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -4904,7 +5070,9 @@
       <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
-      <c r="P85" t="inlineStr"/>
+      <c r="P85" t="n">
+        <v>44</v>
+      </c>
       <c r="Q85" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -4956,10 +5124,12 @@
       <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
-      <c r="P86" t="inlineStr"/>
+      <c r="P86" t="n">
+        <v>33</v>
+      </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>✅ Temiz</t>
+          <t>🚨 RİSKLİ (%24.0)</t>
         </is>
       </c>
       <c r="R86" t="inlineStr"/>
@@ -5008,7 +5178,9 @@
       <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
-      <c r="P87" t="inlineStr"/>
+      <c r="P87" t="n">
+        <v>59</v>
+      </c>
       <c r="Q87" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -5060,7 +5232,9 @@
       <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr"/>
-      <c r="P88" t="inlineStr"/>
+      <c r="P88" t="n">
+        <v>55</v>
+      </c>
       <c r="Q88" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -5112,7 +5286,9 @@
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr"/>
-      <c r="P89" t="inlineStr"/>
+      <c r="P89" t="n">
+        <v>57</v>
+      </c>
       <c r="Q89" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -5164,7 +5340,9 @@
       <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr"/>
-      <c r="P90" t="inlineStr"/>
+      <c r="P90" t="n">
+        <v>49</v>
+      </c>
       <c r="Q90" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -5220,7 +5398,9 @@
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr"/>
-      <c r="P91" t="inlineStr"/>
+      <c r="P91" t="n">
+        <v>70</v>
+      </c>
       <c r="Q91" t="inlineStr">
         <is>
           <t>✅ Finans / Muaf</t>
@@ -5272,10 +5452,12 @@
       <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr"/>
-      <c r="P92" t="inlineStr"/>
+      <c r="P92" t="n">
+        <v>19</v>
+      </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>✅ Temiz</t>
+          <t>⚠️ Dikkat (%9.0)</t>
         </is>
       </c>
       <c r="R92" t="inlineStr"/>
@@ -5324,7 +5506,9 @@
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr"/>
-      <c r="P93" t="inlineStr"/>
+      <c r="P93" t="n">
+        <v>35</v>
+      </c>
       <c r="Q93" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -5376,7 +5560,9 @@
       <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr"/>
-      <c r="P94" t="inlineStr"/>
+      <c r="P94" t="n">
+        <v>38</v>
+      </c>
       <c r="Q94" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -5428,7 +5614,9 @@
       <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr"/>
-      <c r="P95" t="inlineStr"/>
+      <c r="P95" t="n">
+        <v>75</v>
+      </c>
       <c r="Q95" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -5484,7 +5672,9 @@
       <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr"/>
-      <c r="P96" t="inlineStr"/>
+      <c r="P96" t="n">
+        <v>100</v>
+      </c>
       <c r="Q96" t="inlineStr">
         <is>
           <t>✅ Finans / Muaf</t>
@@ -5536,7 +5726,9 @@
       <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr"/>
-      <c r="P97" t="inlineStr"/>
+      <c r="P97" t="n">
+        <v>51</v>
+      </c>
       <c r="Q97" t="inlineStr">
         <is>
           <t>✅ Temiz</t>
@@ -5592,7 +5784,9 @@
       <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr"/>
       <c r="O98" t="inlineStr"/>
-      <c r="P98" t="inlineStr"/>
+      <c r="P98" t="n">
+        <v>40</v>
+      </c>
       <c r="Q98" t="inlineStr">
         <is>
           <t>✅ Finans / Muaf</t>
@@ -5644,10 +5838,12 @@
       <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr"/>
       <c r="O99" t="inlineStr"/>
-      <c r="P99" t="inlineStr"/>
+      <c r="P99" t="n">
+        <v>0</v>
+      </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>✅ Temiz</t>
+          <t>⚠️ Dikkat (%6.1)</t>
         </is>
       </c>
       <c r="R99" t="inlineStr"/>
@@ -5700,7 +5896,9 @@
       <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr"/>
       <c r="O100" t="inlineStr"/>
-      <c r="P100" t="inlineStr"/>
+      <c r="P100" t="n">
+        <v>40</v>
+      </c>
       <c r="Q100" t="inlineStr">
         <is>
           <t>✅ Finans / Muaf</t>
@@ -5752,10 +5950,12 @@
       <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr"/>
       <c r="O101" t="inlineStr"/>
-      <c r="P101" t="inlineStr"/>
+      <c r="P101" t="n">
+        <v>4</v>
+      </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>✅ Temiz</t>
+          <t>⚠️ Dikkat (%10.6)</t>
         </is>
       </c>
       <c r="R101" t="inlineStr"/>

--- a/Temel_Analiz_Omurga.xlsx
+++ b/Temel_Analiz_Omurga.xlsx
@@ -511,7 +511,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,7 +565,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -619,7 +619,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -731,7 +731,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -785,7 +785,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -839,7 +839,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -893,7 +893,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -947,7 +947,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1001,7 +1001,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1059,7 +1059,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1113,7 +1113,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1229,7 +1229,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1283,7 +1283,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1337,7 +1337,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1391,7 +1391,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1445,7 +1445,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1553,7 +1553,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1607,7 +1607,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1661,7 +1661,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1715,7 +1715,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1769,7 +1769,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1823,7 +1823,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1877,7 +1877,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1931,7 +1931,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1985,7 +1985,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2039,7 +2039,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2093,7 +2093,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2147,7 +2147,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2255,7 +2255,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2313,7 +2313,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2367,7 +2367,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2421,7 +2421,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2475,7 +2475,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2529,7 +2529,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2583,7 +2583,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2637,7 +2637,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2649,25 +2649,25 @@
         <v>7</v>
       </c>
       <c r="D41" t="n">
-        <v>4.38</v>
+        <v>4.34</v>
       </c>
       <c r="E41" t="n">
-        <v>0.014</v>
+        <v>0.0148</v>
       </c>
       <c r="F41" t="n">
-        <v>0.0906</v>
+        <v>0.0987</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0263</v>
+        <v>0.0275</v>
       </c>
       <c r="H41" t="n">
-        <v>0.1318</v>
+        <v>0.031</v>
       </c>
       <c r="I41" t="n">
         <v>0.11</v>
       </c>
       <c r="J41" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -2691,7 +2691,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2745,7 +2745,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2799,7 +2799,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2853,7 +2853,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2911,7 +2911,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2965,7 +2965,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3019,7 +3019,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3073,7 +3073,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3082,28 +3082,28 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D49" t="n">
-        <v>6.35</v>
+        <v>6.85</v>
       </c>
       <c r="E49" t="n">
-        <v>0.1046</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="F49" t="n">
-        <v>0.2641</v>
+        <v>0.2716</v>
       </c>
       <c r="G49" t="n">
-        <v>0.2119</v>
+        <v>0.1945</v>
       </c>
       <c r="H49" t="n">
-        <v>0.1372</v>
+        <v>0.1067</v>
       </c>
       <c r="I49" t="n">
-        <v>0.31</v>
+        <v>0.18</v>
       </c>
       <c r="J49" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3181,7 +3181,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3239,7 +3239,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3293,7 +3293,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3351,7 +3351,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3405,7 +3405,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3463,7 +3463,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3517,7 +3517,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3571,7 +3571,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3625,7 +3625,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3679,7 +3679,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3733,7 +3733,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3787,7 +3787,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3841,7 +3841,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3895,7 +3895,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3949,7 +3949,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4003,7 +4003,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4057,7 +4057,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4111,7 +4111,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4165,7 +4165,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4219,7 +4219,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4228,19 +4228,19 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D70" t="n">
         <v>15</v>
       </c>
       <c r="E70" t="n">
-        <v>0.0158</v>
+        <v>0.0404</v>
       </c>
       <c r="F70" t="n">
         <v>1</v>
       </c>
       <c r="G70" t="n">
-        <v>0.0177</v>
+        <v>0.0454</v>
       </c>
       <c r="H70" t="n">
         <v>-5.1853</v>
@@ -4261,7 +4261,7 @@
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4327,7 +4327,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4381,7 +4381,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4435,7 +4435,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4489,7 +4489,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4543,7 +4543,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4597,7 +4597,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4651,7 +4651,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4705,7 +4705,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4759,7 +4759,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4813,7 +4813,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4825,25 +4825,25 @@
         <v>8</v>
       </c>
       <c r="D81" t="n">
-        <v>1.55</v>
+        <v>2.25</v>
       </c>
       <c r="E81" t="n">
-        <v>-0.0042</v>
+        <v>0.0276</v>
       </c>
       <c r="F81" t="n">
-        <v>0.3087</v>
+        <v>0.4023</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.0136</v>
+        <v>0.0859</v>
       </c>
       <c r="H81" t="n">
-        <v>0.1315</v>
+        <v>0.2785</v>
       </c>
       <c r="I81" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="J81" t="n">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -4855,11 +4855,11 @@
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
       <c r="P81" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>⚠️ Dikkat (%7.0)</t>
+          <t>⚠️ Dikkat (%6.3)</t>
         </is>
       </c>
       <c r="R81" t="inlineStr"/>
@@ -4867,7 +4867,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4921,7 +4921,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4975,7 +4975,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5029,7 +5029,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5083,7 +5083,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5137,7 +5137,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5191,7 +5191,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5245,7 +5245,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5299,7 +5299,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5353,7 +5353,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5411,7 +5411,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -5465,7 +5465,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -5519,7 +5519,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -5573,7 +5573,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -5627,7 +5627,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -5685,7 +5685,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -5739,7 +5739,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -5797,7 +5797,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -5851,7 +5851,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -5909,7 +5909,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>26.10.2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">

--- a/Temel_Analiz_Omurga.xlsx
+++ b/Temel_Analiz_Omurga.xlsx
@@ -413,272 +413,212 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R101"/>
+  <dimension ref="A1:L101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Tarih</t>
+          <t>Hisse</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Hisse</t>
+          <t>Piotroski Skoru</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Piotroski Skoru</t>
+          <t>Altman Z</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Altman Z</t>
+          <t>ROA</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>ROA</t>
+          <t>Brüt Marj</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Brüt Marj</t>
+          <t>ROE</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>ROE</t>
+          <t>Net Kar Marjı</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Net Kar Marjı</t>
+          <t>Aktif Devir Hızı</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Aktif Devir Hızı</t>
+          <t>Kaldıraç Oranı</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Kaldıraç Oranı</t>
+          <t>Sektör</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Sektör</t>
+          <t>Temel Skor</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>F/K Oranı</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>PD/DD Oranı</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Değerleme Durumu</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>Pozisyon Durumu</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>Temel Skor</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
           <t>İlişkili Taraf Durumu</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>Prospektif F/K</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
           <t>AEFES</t>
         </is>
       </c>
+      <c r="B2" t="n">
+        <v>7</v>
+      </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>2.61</v>
       </c>
       <c r="D2" t="n">
-        <v>2.61</v>
+        <v>0.0199</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0199</v>
+        <v>0.3944</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3944</v>
+        <v>0.0786</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0786</v>
+        <v>0.0586</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0586</v>
+        <v>0.18</v>
       </c>
       <c r="I2" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="J2" t="n">
         <v>0.21</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>İçecek / Meşrubat</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="n">
+      <c r="K2" t="n">
         <v>47</v>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
           <t>AGHOL</t>
         </is>
       </c>
+      <c r="B3" t="n">
+        <v>7</v>
+      </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>1.49</v>
       </c>
       <c r="D3" t="n">
-        <v>1.49</v>
+        <v>0.0055</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0055</v>
+        <v>0.2865</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2865</v>
+        <v>0.0336</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0336</v>
+        <v>0.0054</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0054</v>
+        <v>0.28</v>
       </c>
       <c r="I3" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="J3" t="n">
         <v>0.22</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="n">
+      <c r="K3" t="n">
         <v>39</v>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
           <t>AHGAZ</t>
         </is>
       </c>
+      <c r="B4" t="n">
+        <v>6</v>
+      </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>7.94</v>
       </c>
       <c r="D4" t="n">
-        <v>7.94</v>
+        <v>0.0212</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0212</v>
+        <v>0.2415</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2415</v>
+        <v>0.0895</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0895</v>
+        <v>0.1053</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1053</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="J4" t="n">
         <v>0.03</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Gaz Dağıtım / Enerji</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="n">
+      <c r="K4" t="n">
         <v>30</v>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>🚨 RİSKLİ (%46.4)</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
+          <t>AKBNK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AKBNK</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -686,19 +626,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D5" t="n">
+        <v>0.0191</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0191</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>0.2286</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2286</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -706,307 +644,249 @@
       <c r="I5" t="n">
         <v>0</v>
       </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Bankacılık</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
+      <c r="K5" t="n">
         <v>40</v>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>✅ Finans / Muaf</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
           <t>AKCNS</t>
         </is>
       </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>7.91</v>
       </c>
       <c r="D6" t="n">
-        <v>7.91</v>
+        <v>0.0141</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0141</v>
+        <v>0.0437</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0437</v>
+        <v>0.0196</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0196</v>
+        <v>0.0283</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0283</v>
+        <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J6" t="n">
         <v>0.11</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Çimento</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="n">
+      <c r="K6" t="n">
         <v>49</v>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
           <t>AKFYE</t>
         </is>
       </c>
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>7.09</v>
       </c>
       <c r="D7" t="n">
-        <v>7.09</v>
+        <v>0.0292</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0292</v>
+        <v>0.1104</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1104</v>
+        <v>0.0365</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0365</v>
+        <v>0.5770999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5770999999999999</v>
+        <v>0.02</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J7" t="n">
         <v>0.15</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Yenilenebilir Enerji</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="n">
+      <c r="K7" t="n">
         <v>57</v>
       </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
           <t>AKSA</t>
         </is>
       </c>
+      <c r="B8" t="n">
+        <v>3</v>
+      </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.1</v>
+        <v>0.0745</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0745</v>
+        <v>0.1476</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1476</v>
+        <v>0.1581</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1581</v>
+        <v>0.1182</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1182</v>
+        <v>0.14</v>
       </c>
       <c r="I8" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="J8" t="n">
         <v>0.37</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>Kimya / Elyaf</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="n">
+      <c r="K8" t="n">
         <v>55</v>
       </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
           <t>AKSEN</t>
         </is>
       </c>
+      <c r="B9" t="n">
+        <v>5</v>
+      </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>1.68</v>
       </c>
       <c r="D9" t="n">
-        <v>1.68</v>
+        <v>0.022</v>
       </c>
       <c r="E9" t="n">
-        <v>0.022</v>
+        <v>0.3472</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3472</v>
+        <v>0.0486</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0486</v>
+        <v>0.0608</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0608</v>
+        <v>0.06</v>
       </c>
       <c r="I9" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="J9" t="n">
         <v>0.42</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Elektrik / Enerji</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="n">
+      <c r="K9" t="n">
         <v>34</v>
       </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
           <t>ALARK</t>
         </is>
       </c>
+      <c r="B10" t="n">
+        <v>8</v>
+      </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>4.3</v>
       </c>
       <c r="D10" t="n">
-        <v>4.3</v>
+        <v>0.0395</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0395</v>
+        <v>0.0587</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0587</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>0.07240000000000001</v>
+        <v>1.2479</v>
       </c>
       <c r="H10" t="n">
-        <v>1.2479</v>
+        <v>0.02</v>
       </c>
       <c r="I10" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J10" t="n">
         <v>0.24</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="n">
+      <c r="K10" t="n">
         <v>64</v>
       </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
+          <t>ALBRK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ALBRK</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1014,19 +894,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D11" t="n">
+        <v>0.0199</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0199</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>0.344</v>
       </c>
       <c r="G11" t="n">
-        <v>0.344</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1034,91 +912,73 @@
       <c r="I11" t="n">
         <v>0</v>
       </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>Bankacılık</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="n">
+      <c r="K11" t="n">
         <v>55</v>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>✅ Finans / Muaf</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
           <t>ALTNY</t>
         </is>
       </c>
+      <c r="B12" t="n">
+        <v>5</v>
+      </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>3.02</v>
       </c>
       <c r="D12" t="n">
-        <v>3.02</v>
+        <v>0.0023</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0023</v>
+        <v>0.2503</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2503</v>
+        <v>0.0054</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0054</v>
+        <v>0.0577</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0577</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="J12" t="n">
         <v>0.21</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>Teknoloji / Savunma</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="n">
+      <c r="K12" t="n">
         <v>49</v>
       </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
+          <t>ANHYT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ANHYT</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1126,19 +986,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D13" t="n">
+        <v>0.0147</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0147</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>0.5911999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5911999999999999</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1146,37 +1004,29 @@
       <c r="I13" t="n">
         <v>0</v>
       </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>Sigorta / Emeklilik</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="n">
+      <c r="K13" t="n">
         <v>70</v>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>✅ Finans / Muaf</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
+          <t>ANSGR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ANSGR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1184,19 +1034,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D14" t="n">
+        <v>0.0914</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0914</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>0.4676</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4676</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1204,485 +1052,395 @@
       <c r="I14" t="n">
         <v>0</v>
       </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>Sigorta</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="n">
+      <c r="K14" t="n">
         <v>100</v>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>✅ Finans / Muaf</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
           <t>ARCLK</t>
         </is>
       </c>
+      <c r="B15" t="n">
+        <v>7</v>
+      </c>
       <c r="C15" t="n">
-        <v>7</v>
+        <v>0.75</v>
       </c>
       <c r="D15" t="n">
-        <v>0.75</v>
+        <v>-0.0057</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.0057</v>
+        <v>0.2935</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2935</v>
+        <v>-0.0435</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0435</v>
+        <v>0.0243</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0243</v>
+        <v>0.24</v>
       </c>
       <c r="I15" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="J15" t="n">
         <v>0.43</v>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>Dayanıklı Tüketim</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="n">
+      <c r="K15" t="n">
         <v>30</v>
       </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
           <t>ASELS</t>
         </is>
       </c>
+      <c r="B16" t="n">
+        <v>4</v>
+      </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>6.36</v>
       </c>
       <c r="D16" t="n">
-        <v>6.36</v>
+        <v>0.0683</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0683</v>
+        <v>0.32</v>
       </c>
       <c r="F16" t="n">
-        <v>0.32</v>
+        <v>0.1225</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1225</v>
+        <v>0.1192</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1192</v>
+        <v>0.13</v>
       </c>
       <c r="I16" t="n">
         <v>0.13</v>
       </c>
-      <c r="J16" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="K16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>Savunma Sanayi</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="n">
+      <c r="K16" t="n">
         <v>57</v>
       </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
           <t>ASTOR</t>
         </is>
       </c>
+      <c r="B17" t="n">
+        <v>6</v>
+      </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>11.86</v>
       </c>
       <c r="D17" t="n">
-        <v>11.86</v>
+        <v>0.1441</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1441</v>
+        <v>0.435</v>
       </c>
       <c r="F17" t="n">
-        <v>0.435</v>
+        <v>0.2323</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2323</v>
+        <v>0.2918</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2918</v>
+        <v>0.13</v>
       </c>
       <c r="I17" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="J17" t="n">
         <v>0.08</v>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>Elektrik Ekipmanları</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="n">
+      <c r="K17" t="n">
         <v>77</v>
       </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
           <t>AYGAZ</t>
         </is>
       </c>
+      <c r="B18" t="n">
+        <v>7</v>
+      </c>
       <c r="C18" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D18" t="n">
-        <v>15</v>
+        <v>0.0511</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0511</v>
+        <v>0.0977</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0977</v>
+        <v>0.0588</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0588</v>
+        <v>0.0241</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0241</v>
+        <v>0.55</v>
       </c>
       <c r="I18" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="J18" t="n">
         <v>0.03</v>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>LPG / Gaz Dağıtım</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="n">
+      <c r="K18" t="n">
         <v>60</v>
       </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
           <t>BERA</t>
         </is>
       </c>
+      <c r="B19" t="n">
+        <v>5</v>
+      </c>
       <c r="C19" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>-0.0077</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0077</v>
+        <v>0.2083</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2083</v>
+        <v>-0.011</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.011</v>
+        <v>0.0256</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0256</v>
+        <v>0.1</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J19" t="n">
         <v>0.02</v>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="n">
+      <c r="K19" t="n">
         <v>40</v>
       </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
           <t>BIMAS</t>
         </is>
       </c>
+      <c r="B20" t="n">
+        <v>6</v>
+      </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>4.74</v>
       </c>
       <c r="D20" t="n">
-        <v>4.74</v>
+        <v>0.0633</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0633</v>
+        <v>0.1923</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1923</v>
+        <v>0.1348</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1348</v>
+        <v>0.0361</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0361</v>
+        <v>0.52</v>
       </c>
       <c r="I20" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="J20" t="n">
         <v>0.15</v>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>Perakende Ticaret</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="n">
+      <c r="K20" t="n">
         <v>57</v>
       </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
           <t>BINHO</t>
         </is>
       </c>
+      <c r="B21" t="n">
+        <v>5</v>
+      </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D21" t="n">
-        <v>15</v>
+        <v>-0.2133</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.2133</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>-0.2849</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2849</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
         <v>0.01</v>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>Teknoloji / Yatırım</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="n">
+      <c r="K21" t="n">
         <v>13</v>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>🚨 RİSKLİ (%24.4)</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
           <t>BRSAN</t>
         </is>
       </c>
+      <c r="B22" t="n">
+        <v>8</v>
+      </c>
       <c r="C22" t="n">
-        <v>8</v>
+        <v>3.52</v>
       </c>
       <c r="D22" t="n">
-        <v>3.52</v>
+        <v>0.0253</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0253</v>
+        <v>0.1342</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1342</v>
+        <v>0.0569</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0569</v>
+        <v>0.0604</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0604</v>
+        <v>0.26</v>
       </c>
       <c r="I22" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="J22" t="n">
         <v>0.17</v>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>Boru / Çelik</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="n">
+      <c r="K22" t="n">
         <v>56</v>
       </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
           <t>BRYAT</t>
         </is>
       </c>
+      <c r="B23" t="n">
+        <v>4</v>
+      </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D23" t="n">
-        <v>15</v>
+        <v>0.1229</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1229</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>0.1311</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1311</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1690,539 +1448,439 @@
       <c r="I23" t="n">
         <v>0</v>
       </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>Borusan Yatırım / Sanayi</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="n">
+      <c r="K23" t="n">
         <v>56</v>
       </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
           <t>BTCIM</t>
         </is>
       </c>
+      <c r="B24" t="n">
+        <v>4</v>
+      </c>
       <c r="C24" t="n">
-        <v>4</v>
+        <v>5.23</v>
       </c>
       <c r="D24" t="n">
-        <v>5.23</v>
+        <v>-0.022</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.022</v>
+        <v>0.1156</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1156</v>
+        <v>-0.0357</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.0357</v>
+        <v>-0.0837</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.0837</v>
+        <v>0.1</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J24" t="n">
         <v>0.14</v>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>Çimento</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="n">
+      <c r="K24" t="n">
         <v>36</v>
       </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
           <t>CANTE</t>
         </is>
       </c>
+      <c r="B25" t="n">
+        <v>6</v>
+      </c>
       <c r="C25" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D25" t="n">
-        <v>15</v>
+        <v>-0.0731</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.0731</v>
+        <v>-0.0297</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.0297</v>
+        <v>-0.0794</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.0794</v>
+        <v>-0.9998</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.9998</v>
+        <v>0.05</v>
       </c>
       <c r="I25" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J25" t="n">
         <v>0.02</v>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>Elektrik Üretimi</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="n">
+      <c r="K25" t="n">
         <v>40</v>
       </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
           <t>CCOLA</t>
         </is>
       </c>
+      <c r="B26" t="n">
+        <v>7</v>
+      </c>
       <c r="C26" t="n">
-        <v>7</v>
+        <v>4.1</v>
       </c>
       <c r="D26" t="n">
-        <v>4.1</v>
+        <v>0.0863</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0863</v>
+        <v>0.3825</v>
       </c>
       <c r="F26" t="n">
-        <v>0.3825</v>
+        <v>0.2262</v>
       </c>
       <c r="G26" t="n">
-        <v>0.2262</v>
+        <v>0.1233</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1233</v>
+        <v>0.28</v>
       </c>
       <c r="I26" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="J26" t="n">
         <v>0.24</v>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>İçecek / Meşrubat</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="n">
+      <c r="K26" t="n">
         <v>71</v>
       </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
           <t>CIMSA</t>
         </is>
       </c>
+      <c r="B27" t="n">
+        <v>6</v>
+      </c>
       <c r="C27" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="D27" t="n">
-        <v>2.4</v>
+        <v>0.037</v>
       </c>
       <c r="E27" t="n">
-        <v>0.037</v>
+        <v>0.2063</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2063</v>
+        <v>0.09810000000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>0.09810000000000001</v>
+        <v>0.1022</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1022</v>
+        <v>0.13</v>
       </c>
       <c r="I27" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="J27" t="n">
         <v>0.31</v>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>Çimento</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="n">
+      <c r="K27" t="n">
         <v>48</v>
       </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
           <t>CVKMD</t>
         </is>
       </c>
+      <c r="B28" t="n">
+        <v>5</v>
+      </c>
       <c r="C28" t="n">
-        <v>5</v>
+        <v>2.74</v>
       </c>
       <c r="D28" t="n">
-        <v>2.74</v>
+        <v>0.014</v>
       </c>
       <c r="E28" t="n">
-        <v>0.014</v>
+        <v>0.3976</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3976</v>
+        <v>0.0299</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0299</v>
+        <v>0.3507</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3507</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="J28" t="n">
         <v>0.16</v>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>Madencilik</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="n">
+      <c r="K28" t="n">
         <v>25</v>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>⚠️ Dikkat (%5.1)</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
           <t>CWENE</t>
         </is>
       </c>
+      <c r="B29" t="n">
+        <v>5</v>
+      </c>
       <c r="C29" t="n">
-        <v>5</v>
+        <v>3.12</v>
       </c>
       <c r="D29" t="n">
-        <v>3.12</v>
+        <v>0.0527</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0527</v>
+        <v>0.2786</v>
       </c>
       <c r="F29" t="n">
-        <v>0.2786</v>
+        <v>0.1229</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1229</v>
+        <v>0.1113</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1113</v>
+        <v>0.11</v>
       </c>
       <c r="I29" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="J29" t="n">
         <v>0.24</v>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>Yenilenebilir Enerji / Güneş</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="n">
+      <c r="K29" t="n">
         <v>34</v>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>🚨 RİSKLİ (%17.9)</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
           <t>DOAS</t>
         </is>
       </c>
+      <c r="B30" t="n">
+        <v>4</v>
+      </c>
       <c r="C30" t="n">
-        <v>4</v>
+        <v>4.56</v>
       </c>
       <c r="D30" t="n">
-        <v>4.56</v>
+        <v>0.0165</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0165</v>
+        <v>0.1166</v>
       </c>
       <c r="F30" t="n">
-        <v>0.1166</v>
+        <v>0.034</v>
       </c>
       <c r="G30" t="n">
-        <v>0.034</v>
+        <v>0.029</v>
       </c>
       <c r="H30" t="n">
-        <v>0.029</v>
+        <v>0.39</v>
       </c>
       <c r="I30" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="J30" t="n">
         <v>0.22</v>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>Otomotiv Dağıtım</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="n">
+      <c r="K30" t="n">
         <v>22</v>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>🚨 RİSKLİ (%17.5)</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
           <t>DOHOL</t>
         </is>
       </c>
+      <c r="B31" t="n">
+        <v>6</v>
+      </c>
       <c r="C31" t="n">
-        <v>6</v>
+        <v>3.93</v>
       </c>
       <c r="D31" t="n">
-        <v>3.93</v>
+        <v>0.0269</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0269</v>
+        <v>0.2086</v>
       </c>
       <c r="F31" t="n">
-        <v>0.2086</v>
+        <v>0.0621</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0621</v>
+        <v>0.1255</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1255</v>
+        <v>0.12</v>
       </c>
       <c r="I31" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="J31" t="n">
         <v>0.2</v>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="n">
+      <c r="K31" t="n">
         <v>30</v>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>⚠️ Dikkat (%14.9)</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
           <t>ECILC</t>
         </is>
       </c>
+      <c r="B32" t="n">
+        <v>5</v>
+      </c>
       <c r="C32" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D32" t="n">
-        <v>15</v>
+        <v>-0.0197</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.0197</v>
+        <v>0.3779</v>
       </c>
       <c r="F32" t="n">
-        <v>0.3779</v>
+        <v>-0.0243</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.0243</v>
+        <v>-0.3397</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.3397</v>
+        <v>0.03</v>
       </c>
       <c r="I32" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="J32" t="n">
         <v>0.05</v>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>İlaç / Sağlık</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="n">
+      <c r="K32" t="n">
         <v>38</v>
       </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
           <t>ECZYT</t>
         </is>
       </c>
+      <c r="B33" t="n">
+        <v>2</v>
+      </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D33" t="n">
-        <v>15</v>
+        <v>-0.0132</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.0132</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>-0.0135</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.0135</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -2230,37 +1888,29 @@
       <c r="I33" t="n">
         <v>0</v>
       </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>Holding / Yatırım</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="n">
+      <c r="K33" t="n">
         <v>31</v>
       </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
+          <t>EGEEN</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>EGEEN</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2268,10 +1918,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D34" t="n">
+        <v>0</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -2288,577 +1936,469 @@
       <c r="I34" t="n">
         <v>0</v>
       </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>Otomotiv Yan Sanayi</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr"/>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
           <t>EGGUB</t>
         </is>
       </c>
+      <c r="B35" t="n">
+        <v>6</v>
+      </c>
       <c r="C35" t="n">
-        <v>6</v>
+        <v>10.31</v>
       </c>
       <c r="D35" t="n">
-        <v>10.31</v>
+        <v>0.0564</v>
       </c>
       <c r="E35" t="n">
-        <v>0.0564</v>
+        <v>0.5342</v>
       </c>
       <c r="F35" t="n">
-        <v>0.5342</v>
+        <v>0.0701</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0701</v>
+        <v>0.1822</v>
       </c>
       <c r="H35" t="n">
-        <v>0.1822</v>
+        <v>0.09</v>
       </c>
       <c r="I35" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="J35" t="n">
         <v>0.11</v>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>Gübre / Limancılık</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="n">
+      <c r="K35" t="n">
         <v>65</v>
       </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
           <t>EKGYO</t>
         </is>
       </c>
+      <c r="B36" t="n">
+        <v>3</v>
+      </c>
       <c r="C36" t="n">
-        <v>3</v>
+        <v>5.11</v>
       </c>
       <c r="D36" t="n">
-        <v>5.11</v>
+        <v>-0.0043</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.0043</v>
+        <v>0.2784</v>
       </c>
       <c r="F36" t="n">
-        <v>0.2784</v>
+        <v>-0.0122</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.0122</v>
+        <v>0.0329</v>
       </c>
       <c r="H36" t="n">
-        <v>0.0329</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="J36" t="n">
         <v>0.22</v>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>Gayrimenkul Yatırım Ort.</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="n">
+      <c r="K36" t="n">
         <v>36</v>
       </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
           <t>ENERY</t>
         </is>
       </c>
+      <c r="B37" t="n">
+        <v>4</v>
+      </c>
       <c r="C37" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D37" t="n">
-        <v>15</v>
+        <v>0.0445</v>
       </c>
       <c r="E37" t="n">
-        <v>0.0445</v>
+        <v>0.0835</v>
       </c>
       <c r="F37" t="n">
-        <v>0.0835</v>
+        <v>0.0833</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0833</v>
+        <v>0.2279</v>
       </c>
       <c r="H37" t="n">
-        <v>0.2279</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="J37" t="n">
         <v>0.03</v>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>Gaz Dağıtım / Enerji</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="n">
+      <c r="K37" t="n">
         <v>55</v>
       </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
           <t>ENJSA</t>
         </is>
       </c>
+      <c r="B38" t="n">
+        <v>7</v>
+      </c>
       <c r="C38" t="n">
-        <v>7</v>
+        <v>1.69</v>
       </c>
       <c r="D38" t="n">
-        <v>1.69</v>
+        <v>0.0219</v>
       </c>
       <c r="E38" t="n">
-        <v>0.0219</v>
+        <v>0.3094</v>
       </c>
       <c r="F38" t="n">
-        <v>0.3094</v>
+        <v>0.0557</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0557</v>
+        <v>0.0274</v>
       </c>
       <c r="H38" t="n">
-        <v>0.0274</v>
+        <v>0.21</v>
       </c>
       <c r="I38" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="J38" t="n">
         <v>0.34</v>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>Elektrik Dağıtım / Enerji</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="n">
+      <c r="K38" t="n">
         <v>14</v>
       </c>
-      <c r="Q38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>⚠️ Dikkat (%13.7)</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
           <t>ENKAI</t>
         </is>
       </c>
+      <c r="B39" t="n">
+        <v>6</v>
+      </c>
       <c r="C39" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D39" t="n">
-        <v>15</v>
+        <v>0.0721</v>
       </c>
       <c r="E39" t="n">
-        <v>0.0721</v>
+        <v>0.1745</v>
       </c>
       <c r="F39" t="n">
-        <v>0.1745</v>
+        <v>0.0953</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0953</v>
+        <v>0.3106</v>
       </c>
       <c r="H39" t="n">
-        <v>0.3106</v>
+        <v>0.09</v>
       </c>
       <c r="I39" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="J39" t="n">
         <v>0.01</v>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>İnşaat / Taahhüt / Enerji</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="n">
+      <c r="K39" t="n">
         <v>65</v>
       </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
           <t>ENTRA</t>
         </is>
       </c>
+      <c r="B40" t="n">
+        <v>5</v>
+      </c>
       <c r="C40" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="D40" t="n">
-        <v>4.1</v>
+        <v>-0.0212</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.0212</v>
+        <v>0.2009</v>
       </c>
       <c r="F40" t="n">
-        <v>0.2009</v>
+        <v>-0.0284</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.0284</v>
+        <v>0.1922</v>
       </c>
       <c r="H40" t="n">
-        <v>0.1922</v>
+        <v>0.02</v>
       </c>
       <c r="I40" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J40" t="n">
         <v>0.2</v>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>Yenilenebilir Enerji</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="n">
+      <c r="K40" t="n">
         <v>23</v>
       </c>
-      <c r="Q40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>⚠️ Dikkat (%5.9)</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
           <t>EREGL</t>
         </is>
       </c>
+      <c r="B41" t="n">
+        <v>7</v>
+      </c>
       <c r="C41" t="n">
-        <v>7</v>
+        <v>4.34</v>
       </c>
       <c r="D41" t="n">
-        <v>4.34</v>
+        <v>0.0148</v>
       </c>
       <c r="E41" t="n">
-        <v>0.0148</v>
+        <v>0.0987</v>
       </c>
       <c r="F41" t="n">
-        <v>0.0987</v>
+        <v>0.0275</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0275</v>
+        <v>0.031</v>
       </c>
       <c r="H41" t="n">
-        <v>0.031</v>
+        <v>0.11</v>
       </c>
       <c r="I41" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="J41" t="n">
         <v>0.26</v>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>Demir Çelik</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="n">
+      <c r="K41" t="n">
         <v>54</v>
       </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
           <t>EUREN</t>
         </is>
       </c>
+      <c r="B42" t="n">
+        <v>6</v>
+      </c>
       <c r="C42" t="n">
-        <v>6</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="D42" t="n">
-        <v>8.109999999999999</v>
+        <v>0.0042</v>
       </c>
       <c r="E42" t="n">
-        <v>0.0042</v>
+        <v>0.0958</v>
       </c>
       <c r="F42" t="n">
-        <v>0.0958</v>
+        <v>0.0058</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0058</v>
+        <v>0.0167</v>
       </c>
       <c r="H42" t="n">
-        <v>0.0167</v>
+        <v>0.14</v>
       </c>
       <c r="I42" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="J42" t="n">
         <v>0.12</v>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>Cam / Yapı Malzemeleri</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="n">
+      <c r="K42" t="n">
         <v>51</v>
       </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
           <t>FENER</t>
         </is>
       </c>
+      <c r="B43" t="n">
+        <v>5</v>
+      </c>
       <c r="C43" t="n">
-        <v>5</v>
+        <v>-3.72</v>
       </c>
       <c r="D43" t="n">
-        <v>-3.72</v>
+        <v>-0.0333</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.0333</v>
+        <v>-0.4124</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.4124</v>
+        <v>1.6847</v>
       </c>
       <c r="G43" t="n">
-        <v>1.6847</v>
+        <v>-0.0525</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.0525</v>
+        <v>0.16</v>
       </c>
       <c r="I43" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="J43" t="n">
         <v>0.19</v>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>Spor Kulübü</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="n">
+      <c r="K43" t="n">
         <v>18</v>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>🚨 RİSKLİ (%50.3)</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
           <t>FROTO</t>
         </is>
       </c>
+      <c r="B44" t="n">
+        <v>4</v>
+      </c>
       <c r="C44" t="n">
-        <v>4</v>
+        <v>3.24</v>
       </c>
       <c r="D44" t="n">
-        <v>3.24</v>
+        <v>0.0606</v>
       </c>
       <c r="E44" t="n">
-        <v>0.0606</v>
+        <v>0.0683</v>
       </c>
       <c r="F44" t="n">
-        <v>0.0683</v>
+        <v>0.1654</v>
       </c>
       <c r="G44" t="n">
-        <v>0.1654</v>
+        <v>0.0201</v>
       </c>
       <c r="H44" t="n">
-        <v>0.0201</v>
+        <v>0.45</v>
       </c>
       <c r="I44" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="J44" t="n">
         <v>0.34</v>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>Otomotiv Üretim</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="n">
+      <c r="K44" t="n">
         <v>60</v>
       </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
+          <t>GARAN</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>GARAN</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2866,19 +2406,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D45" t="n">
+        <v>0.027</v>
       </c>
       <c r="E45" t="n">
-        <v>0.027</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>0.2813</v>
       </c>
       <c r="G45" t="n">
-        <v>0.2813</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -2886,307 +2424,249 @@
       <c r="I45" t="n">
         <v>0</v>
       </c>
-      <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>Bankacılık</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="n">
+      <c r="K45" t="n">
         <v>70</v>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>✅ Finans / Muaf</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
           <t>GLRMK</t>
         </is>
       </c>
+      <c r="B46" t="n">
+        <v>3</v>
+      </c>
       <c r="C46" t="n">
-        <v>3</v>
+        <v>5.98</v>
       </c>
       <c r="D46" t="n">
-        <v>5.98</v>
+        <v>0.0456</v>
       </c>
       <c r="E46" t="n">
-        <v>0.0456</v>
+        <v>0.1244</v>
       </c>
       <c r="F46" t="n">
-        <v>0.1244</v>
+        <v>0.1285</v>
       </c>
       <c r="G46" t="n">
-        <v>0.1285</v>
+        <v>0.1045</v>
       </c>
       <c r="H46" t="n">
-        <v>0.1045</v>
+        <v>0.15</v>
       </c>
       <c r="I46" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="J46" t="n">
         <v>0.22</v>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>İnşaat / Ağır Sanayi</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="n">
+      <c r="K46" t="n">
         <v>24</v>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>🚨 RİSKLİ (%51.8)</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
           <t>GLYHO</t>
         </is>
       </c>
+      <c r="B47" t="n">
+        <v>6</v>
+      </c>
       <c r="C47" t="n">
-        <v>6</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D47" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.0504</v>
       </c>
       <c r="E47" t="n">
-        <v>0.0504</v>
+        <v>0.4455</v>
       </c>
       <c r="F47" t="n">
-        <v>0.4455</v>
+        <v>0.3473</v>
       </c>
       <c r="G47" t="n">
-        <v>0.3473</v>
+        <v>0.1889</v>
       </c>
       <c r="H47" t="n">
-        <v>0.1889</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I47" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="J47" t="n">
         <v>0.67</v>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="n">
+      <c r="K47" t="n">
         <v>60</v>
       </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
           <t>GRSEL</t>
         </is>
       </c>
+      <c r="B48" t="n">
+        <v>6</v>
+      </c>
       <c r="C48" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D48" t="n">
-        <v>15</v>
+        <v>0.1697</v>
       </c>
       <c r="E48" t="n">
-        <v>0.1697</v>
+        <v>0.3296</v>
       </c>
       <c r="F48" t="n">
-        <v>0.3296</v>
+        <v>0.213</v>
       </c>
       <c r="G48" t="n">
-        <v>0.213</v>
+        <v>0.2555</v>
       </c>
       <c r="H48" t="n">
-        <v>0.2555</v>
+        <v>0.18</v>
       </c>
       <c r="I48" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="J48" t="n">
         <v>0.02</v>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>Taşımacılık / Ulaştırma</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="n">
+      <c r="K48" t="n">
         <v>77</v>
       </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
           <t>GUBRF</t>
         </is>
       </c>
+      <c r="B49" t="n">
+        <v>5</v>
+      </c>
       <c r="C49" t="n">
-        <v>5</v>
+        <v>6.85</v>
       </c>
       <c r="D49" t="n">
-        <v>6.85</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="E49" t="n">
-        <v>0.09719999999999999</v>
+        <v>0.2716</v>
       </c>
       <c r="F49" t="n">
-        <v>0.2716</v>
+        <v>0.1945</v>
       </c>
       <c r="G49" t="n">
-        <v>0.1945</v>
+        <v>0.1067</v>
       </c>
       <c r="H49" t="n">
-        <v>0.1067</v>
+        <v>0.18</v>
       </c>
       <c r="I49" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="J49" t="n">
         <v>0.12</v>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>Kimyevi Gübre</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="n">
+      <c r="K49" t="n">
         <v>66</v>
       </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
           <t>GWIND</t>
         </is>
       </c>
+      <c r="B50" t="n">
+        <v>4</v>
+      </c>
       <c r="C50" t="n">
-        <v>4</v>
+        <v>7.38</v>
       </c>
       <c r="D50" t="n">
-        <v>7.38</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="E50" t="n">
-        <v>0.09180000000000001</v>
+        <v>-0.0271</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.0271</v>
+        <v>0.1206</v>
       </c>
       <c r="G50" t="n">
-        <v>0.1206</v>
+        <v>4.3607</v>
       </c>
       <c r="H50" t="n">
-        <v>4.3607</v>
+        <v>0.02</v>
       </c>
       <c r="I50" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J50" t="n">
         <v>0.14</v>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>Yenilenebilir Enerji</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="n">
+      <c r="K50" t="n">
         <v>61</v>
       </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
+          <t>HALKB</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>HALKB</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3194,19 +2674,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D51" t="n">
+        <v>0.0076</v>
       </c>
       <c r="E51" t="n">
-        <v>0.0076</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>0.1531</v>
       </c>
       <c r="G51" t="n">
-        <v>0.1531</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -3214,91 +2692,73 @@
       <c r="I51" t="n">
         <v>0</v>
       </c>
-      <c r="J51" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>Bankacılık</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="n">
+      <c r="K51" t="n">
         <v>25</v>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>✅ Finans / Muaf</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
           <t>HEKTS</t>
         </is>
       </c>
+      <c r="B52" t="n">
+        <v>5</v>
+      </c>
       <c r="C52" t="n">
-        <v>5</v>
+        <v>-0.43</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.43</v>
+        <v>-0.1386</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.1386</v>
+        <v>0.1639</v>
       </c>
       <c r="F52" t="n">
-        <v>0.1639</v>
+        <v>-0.2913</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.2913</v>
+        <v>-0.8646</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.8646</v>
+        <v>0.06</v>
       </c>
       <c r="I52" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="J52" t="n">
         <v>0.38</v>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>Tarım Kimyasalları</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="n">
+      <c r="K52" t="n">
         <v>23</v>
       </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
+          <t>ISCTR</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ISCTR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3306,19 +2766,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D53" t="n">
+        <v>0.0171</v>
       </c>
       <c r="E53" t="n">
-        <v>0.0171</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>0.189</v>
       </c>
       <c r="G53" t="n">
-        <v>0.189</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -3326,91 +2784,73 @@
       <c r="I53" t="n">
         <v>0</v>
       </c>
-      <c r="J53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>Bankacılık</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="n">
+      <c r="K53" t="n">
         <v>40</v>
       </c>
-      <c r="Q53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>✅ Finans / Muaf</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
           <t>ISDMR</t>
         </is>
       </c>
+      <c r="B54" t="n">
+        <v>7</v>
+      </c>
       <c r="C54" t="n">
-        <v>7</v>
+        <v>6.24</v>
       </c>
       <c r="D54" t="n">
-        <v>6.24</v>
+        <v>0.0516</v>
       </c>
       <c r="E54" t="n">
-        <v>0.0516</v>
+        <v>0.09</v>
       </c>
       <c r="F54" t="n">
-        <v>0.09</v>
+        <v>0.0815</v>
       </c>
       <c r="G54" t="n">
-        <v>0.0815</v>
+        <v>0.2135</v>
       </c>
       <c r="H54" t="n">
-        <v>0.2135</v>
+        <v>0.15</v>
       </c>
       <c r="I54" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="J54" t="n">
         <v>0.16</v>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>Demir Çelik</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="n">
+      <c r="K54" t="n">
         <v>68</v>
       </c>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
+          <t>ISMEN</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISMEN</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3418,19 +2858,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D55" t="n">
+        <v>0.0409</v>
       </c>
       <c r="E55" t="n">
-        <v>0.0409</v>
+        <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>0.1572</v>
       </c>
       <c r="G55" t="n">
-        <v>0.1572</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -3438,1927 +2876,1569 @@
       <c r="I55" t="n">
         <v>0</v>
       </c>
-      <c r="J55" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>Aracı Kurum / Menkul Değer</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="n">
+      <c r="K55" t="n">
         <v>70</v>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>✅ Finans / Muaf</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
           <t>KARSN</t>
         </is>
       </c>
+      <c r="B56" t="n">
+        <v>5</v>
+      </c>
       <c r="C56" t="n">
-        <v>5</v>
+        <v>-0.41</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.41</v>
+        <v>0.0108</v>
       </c>
       <c r="E56" t="n">
-        <v>0.0108</v>
+        <v>0.1985</v>
       </c>
       <c r="F56" t="n">
-        <v>0.1985</v>
+        <v>0.0295</v>
       </c>
       <c r="G56" t="n">
-        <v>0.0295</v>
+        <v>-0.0653</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.0653</v>
+        <v>0.22</v>
       </c>
       <c r="I56" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="J56" t="n">
         <v>0.42</v>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>Otomotiv Üretim</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="n">
+      <c r="K56" t="n">
         <v>32</v>
       </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
           <t>KATMR</t>
         </is>
       </c>
+      <c r="B57" t="n">
+        <v>3</v>
+      </c>
       <c r="C57" t="n">
-        <v>3</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="D57" t="n">
-        <v>9.029999999999999</v>
+        <v>0.0325</v>
       </c>
       <c r="E57" t="n">
-        <v>0.0325</v>
+        <v>0.2154</v>
       </c>
       <c r="F57" t="n">
-        <v>0.2154</v>
+        <v>0.0458</v>
       </c>
       <c r="G57" t="n">
-        <v>0.0458</v>
+        <v>-0.2217</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.2217</v>
+        <v>0.06</v>
       </c>
       <c r="I57" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="J57" t="n">
         <v>0.16</v>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>Araç Üstü Ekipman / Savunma</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="n">
+      <c r="K57" t="n">
         <v>43</v>
       </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
           <t>KCAER</t>
         </is>
       </c>
+      <c r="B58" t="n">
+        <v>5</v>
+      </c>
       <c r="C58" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="D58" t="n">
-        <v>3.4</v>
+        <v>0.0208</v>
       </c>
       <c r="E58" t="n">
-        <v>0.0208</v>
+        <v>0.2309</v>
       </c>
       <c r="F58" t="n">
-        <v>0.2309</v>
+        <v>0.0443</v>
       </c>
       <c r="G58" t="n">
-        <v>0.0443</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="H58" t="n">
-        <v>0.07829999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="I58" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J58" t="n">
         <v>0.27</v>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>Çelik Profil</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="n">
+      <c r="K58" t="n">
         <v>53</v>
       </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
           <t>KCHOL</t>
         </is>
       </c>
+      <c r="B59" t="n">
+        <v>5</v>
+      </c>
       <c r="C59" t="n">
-        <v>5</v>
+        <v>0.54</v>
       </c>
       <c r="D59" t="n">
-        <v>0.54</v>
+        <v>0.0057</v>
       </c>
       <c r="E59" t="n">
-        <v>0.0057</v>
+        <v>0.1846</v>
       </c>
       <c r="F59" t="n">
-        <v>0.1846</v>
+        <v>0.0449</v>
       </c>
       <c r="G59" t="n">
-        <v>0.0449</v>
+        <v>0.0218</v>
       </c>
       <c r="H59" t="n">
-        <v>0.0218</v>
+        <v>0.15</v>
       </c>
       <c r="I59" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="J59" t="n">
         <v>0.28</v>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="n">
+      <c r="K59" t="n">
         <v>9</v>
       </c>
-      <c r="Q59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t>🚨 RİSKLİ (%45.4)</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
           <t>KORDS</t>
         </is>
       </c>
+      <c r="B60" t="n">
+        <v>6</v>
+      </c>
       <c r="C60" t="n">
-        <v>6</v>
+        <v>1.64</v>
       </c>
       <c r="D60" t="n">
-        <v>1.64</v>
+        <v>-0.0081</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.0081</v>
+        <v>0.1971</v>
       </c>
       <c r="F60" t="n">
-        <v>0.1971</v>
+        <v>-0.0252</v>
       </c>
       <c r="G60" t="n">
-        <v>-0.0252</v>
+        <v>0.0569</v>
       </c>
       <c r="H60" t="n">
-        <v>0.0569</v>
+        <v>0.18</v>
       </c>
       <c r="I60" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="J60" t="n">
         <v>0.36</v>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>Endüstriyel İplik / Kord Bezi</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="n">
+      <c r="K60" t="n">
         <v>27</v>
       </c>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
           <t>KRDMD</t>
         </is>
       </c>
+      <c r="B61" t="n">
+        <v>7</v>
+      </c>
       <c r="C61" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D61" t="n">
-        <v>15</v>
+        <v>0.0297</v>
       </c>
       <c r="E61" t="n">
-        <v>0.0297</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="F61" t="n">
-        <v>0.09619999999999999</v>
+        <v>0.0422</v>
       </c>
       <c r="G61" t="n">
-        <v>0.0422</v>
+        <v>0.2861</v>
       </c>
       <c r="H61" t="n">
-        <v>0.2861</v>
+        <v>0.14</v>
       </c>
       <c r="I61" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="J61" t="n">
         <v>0.05</v>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>Demir Çelik</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="n">
+      <c r="K61" t="n">
         <v>62</v>
       </c>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
           <t>LMKDC</t>
         </is>
       </c>
+      <c r="B62" t="n">
+        <v>3</v>
+      </c>
       <c r="C62" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D62" t="n">
-        <v>15</v>
+        <v>0.1665</v>
       </c>
       <c r="E62" t="n">
-        <v>0.1665</v>
+        <v>0.3307</v>
       </c>
       <c r="F62" t="n">
-        <v>0.3307</v>
+        <v>0.2049</v>
       </c>
       <c r="G62" t="n">
-        <v>0.2049</v>
+        <v>0.2325</v>
       </c>
       <c r="H62" t="n">
-        <v>0.2325</v>
+        <v>0.22</v>
       </c>
       <c r="I62" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="J62" t="n">
         <v>0.01</v>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>Çimento</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="n">
+      <c r="K62" t="n">
         <v>71</v>
       </c>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
           <t>MAVI</t>
         </is>
       </c>
+      <c r="B63" t="n">
+        <v>5</v>
+      </c>
       <c r="C63" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="D63" t="n">
-        <v>5.3</v>
+        <v>0.063</v>
       </c>
       <c r="E63" t="n">
-        <v>0.063</v>
+        <v>0.5283</v>
       </c>
       <c r="F63" t="n">
-        <v>0.5283</v>
+        <v>0.134</v>
       </c>
       <c r="G63" t="n">
-        <v>0.134</v>
+        <v>0.021</v>
       </c>
       <c r="H63" t="n">
-        <v>0.021</v>
+        <v>0.39</v>
       </c>
       <c r="I63" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="J63" t="n">
         <v>0.19</v>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t>Tekstil / Hazır Giyim</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="n">
+      <c r="K63" t="n">
         <v>55</v>
       </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
           <t>MGROS</t>
         </is>
       </c>
+      <c r="B64" t="n">
+        <v>4</v>
+      </c>
       <c r="C64" t="n">
-        <v>4</v>
+        <v>3.22</v>
       </c>
       <c r="D64" t="n">
-        <v>3.22</v>
+        <v>0.0238</v>
       </c>
       <c r="E64" t="n">
-        <v>0.0238</v>
+        <v>0.2268</v>
       </c>
       <c r="F64" t="n">
-        <v>0.2268</v>
+        <v>0.064</v>
       </c>
       <c r="G64" t="n">
-        <v>0.064</v>
+        <v>-0.0056</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.0056</v>
+        <v>0.5</v>
       </c>
       <c r="I64" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J64" t="n">
         <v>0.16</v>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>Perakende Ticaret</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="n">
+      <c r="K64" t="n">
         <v>45</v>
       </c>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
           <t>MPARK</t>
         </is>
       </c>
+      <c r="B65" t="n">
+        <v>5</v>
+      </c>
       <c r="C65" t="n">
-        <v>5</v>
+        <v>3.25</v>
       </c>
       <c r="D65" t="n">
-        <v>3.25</v>
+        <v>0.0617</v>
       </c>
       <c r="E65" t="n">
-        <v>0.0617</v>
+        <v>0.2475</v>
       </c>
       <c r="F65" t="n">
-        <v>0.2475</v>
+        <v>0.1341</v>
       </c>
       <c r="G65" t="n">
-        <v>0.1341</v>
+        <v>0.0818</v>
       </c>
       <c r="H65" t="n">
-        <v>0.0818</v>
+        <v>0.18</v>
       </c>
       <c r="I65" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="J65" t="n">
         <v>0.23</v>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>Sağlık Hizmetleri</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="n">
+      <c r="K65" t="n">
         <v>34</v>
       </c>
-      <c r="Q65" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t>🚨 RİSKLİ (%16.2)</t>
         </is>
       </c>
-      <c r="R65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
           <t>OBAMS</t>
         </is>
       </c>
+      <c r="B66" t="n">
+        <v>6</v>
+      </c>
       <c r="C66" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D66" t="n">
-        <v>15</v>
+        <v>-0.1106</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.1106</v>
+        <v>0.0958</v>
       </c>
       <c r="F66" t="n">
-        <v>0.0958</v>
+        <v>-0.1343</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.1343</v>
+        <v>0.1265</v>
       </c>
       <c r="H66" t="n">
-        <v>0.1265</v>
+        <v>0.47</v>
       </c>
       <c r="I66" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="J66" t="n">
-        <v>0</v>
-      </c>
-      <c r="K66" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J66" t="inlineStr">
         <is>
           <t>Gıda Üretimi</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="n">
+      <c r="K66" t="n">
         <v>46</v>
       </c>
-      <c r="Q66" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
           <t>ODAS</t>
         </is>
       </c>
+      <c r="B67" t="n">
+        <v>5</v>
+      </c>
       <c r="C67" t="n">
-        <v>5</v>
+        <v>10.47</v>
       </c>
       <c r="D67" t="n">
-        <v>10.47</v>
+        <v>-0.0064</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.0064</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="F67" t="n">
-        <v>0.07969999999999999</v>
+        <v>-0.0186</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.0186</v>
+        <v>-0.4046</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.4046</v>
+        <v>0.05</v>
       </c>
       <c r="I67" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J67" t="n">
         <v>0.04</v>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t>Elektrik Üretimi / Madencilik</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="n">
+      <c r="K67" t="n">
         <v>13</v>
       </c>
-      <c r="Q67" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t>⚠️ Dikkat (%6.0)</t>
         </is>
       </c>
-      <c r="R67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
           <t>OTKAR</t>
         </is>
       </c>
+      <c r="B68" t="n">
+        <v>2</v>
+      </c>
       <c r="C68" t="n">
-        <v>2</v>
+        <v>1.08</v>
       </c>
       <c r="D68" t="n">
-        <v>1.08</v>
+        <v>-0.0633</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.0633</v>
+        <v>0.1302</v>
       </c>
       <c r="F68" t="n">
-        <v>0.1302</v>
+        <v>-0.8821</v>
       </c>
       <c r="G68" t="n">
-        <v>-0.8821</v>
+        <v>-0.2538</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.2538</v>
+        <v>0.14</v>
       </c>
       <c r="I68" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="J68" t="n">
         <v>0.63</v>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t>Otomotiv / Savunma</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
-      <c r="P68" t="n">
+      <c r="K68" t="n">
         <v>11</v>
       </c>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
           <t>OYAKC</t>
         </is>
       </c>
+      <c r="B69" t="n">
+        <v>6</v>
+      </c>
       <c r="C69" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D69" t="n">
-        <v>15</v>
+        <v>0.0757</v>
       </c>
       <c r="E69" t="n">
-        <v>0.0757</v>
+        <v>0.2549</v>
       </c>
       <c r="F69" t="n">
-        <v>0.2549</v>
+        <v>0.0927</v>
       </c>
       <c r="G69" t="n">
-        <v>0.0927</v>
+        <v>0.1337</v>
       </c>
       <c r="H69" t="n">
-        <v>0.1337</v>
+        <v>0.17</v>
       </c>
       <c r="I69" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="J69" t="n">
         <v>0.03</v>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t>Çimento</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="n">
+      <c r="K69" t="n">
         <v>61</v>
       </c>
-      <c r="Q69" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
           <t>PAHOL</t>
         </is>
       </c>
+      <c r="B70" t="n">
+        <v>4</v>
+      </c>
       <c r="C70" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D70" t="n">
-        <v>15</v>
+        <v>0.0404</v>
       </c>
       <c r="E70" t="n">
-        <v>0.0404</v>
+        <v>1</v>
       </c>
       <c r="F70" t="n">
-        <v>1</v>
+        <v>0.0454</v>
       </c>
       <c r="G70" t="n">
-        <v>0.0454</v>
+        <v>-5.1853</v>
       </c>
       <c r="H70" t="n">
-        <v>-5.1853</v>
+        <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" t="n">
         <v>0.01</v>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
-      <c r="P70" t="n">
+      <c r="K70" t="n">
         <v>20</v>
       </c>
-      <c r="Q70" t="inlineStr">
+      <c r="L70" t="inlineStr">
         <is>
           <t>🚨 RİSKLİ (%95.7)</t>
         </is>
       </c>
-      <c r="R70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
           <t>PETKM</t>
         </is>
       </c>
+      <c r="B71" t="n">
+        <v>7</v>
+      </c>
       <c r="C71" t="n">
-        <v>7</v>
+        <v>1.23</v>
       </c>
       <c r="D71" t="n">
-        <v>1.23</v>
+        <v>-0.0126</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.0126</v>
+        <v>0.0858</v>
       </c>
       <c r="F71" t="n">
-        <v>0.0858</v>
+        <v>-0.0305</v>
       </c>
       <c r="G71" t="n">
-        <v>-0.0305</v>
+        <v>0.1119</v>
       </c>
       <c r="H71" t="n">
-        <v>0.1119</v>
+        <v>0.2</v>
       </c>
       <c r="I71" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J71" t="n">
         <v>0.26</v>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t>Petrokimya</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
-      <c r="P71" t="n">
+      <c r="K71" t="n">
         <v>34</v>
       </c>
-      <c r="Q71" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
           <t>PGSUS</t>
         </is>
       </c>
+      <c r="B72" t="n">
+        <v>3</v>
+      </c>
       <c r="C72" t="n">
-        <v>3</v>
+        <v>0.48</v>
       </c>
       <c r="D72" t="n">
-        <v>0.48</v>
+        <v>-0.0039</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.0039</v>
+        <v>0.02</v>
       </c>
       <c r="F72" t="n">
-        <v>0.02</v>
+        <v>-0.0153</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.0153</v>
+        <v>-0.1049</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.1049</v>
+        <v>0.1</v>
       </c>
       <c r="I72" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J72" t="n">
         <v>0.58</v>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t>Ulaştırma / Havacılık</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
-      <c r="P72" t="n">
+      <c r="K72" t="n">
         <v>14</v>
       </c>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
           <t>RGYAS</t>
         </is>
       </c>
+      <c r="B73" t="n">
+        <v>5</v>
+      </c>
       <c r="C73" t="n">
-        <v>5</v>
+        <v>7.05</v>
       </c>
       <c r="D73" t="n">
-        <v>7.05</v>
+        <v>0.0834</v>
       </c>
       <c r="E73" t="n">
-        <v>0.0834</v>
+        <v>0.6899</v>
       </c>
       <c r="F73" t="n">
-        <v>0.6899</v>
+        <v>0.1216</v>
       </c>
       <c r="G73" t="n">
-        <v>0.1216</v>
+        <v>0.9392</v>
       </c>
       <c r="H73" t="n">
-        <v>0.9392</v>
+        <v>0.02</v>
       </c>
       <c r="I73" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J73" t="n">
         <v>0.15</v>
       </c>
-      <c r="K73" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t>Gayrimenkul Yatırım Ort.</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr"/>
-      <c r="P73" t="n">
+      <c r="K73" t="n">
         <v>63</v>
       </c>
-      <c r="Q73" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
           <t>RYSAS</t>
         </is>
       </c>
+      <c r="B74" t="n">
+        <v>6</v>
+      </c>
       <c r="C74" t="n">
-        <v>6</v>
+        <v>4.65</v>
       </c>
       <c r="D74" t="n">
-        <v>4.65</v>
+        <v>0.0668</v>
       </c>
       <c r="E74" t="n">
-        <v>0.0668</v>
+        <v>0.3002</v>
       </c>
       <c r="F74" t="n">
-        <v>0.3002</v>
+        <v>0.123</v>
       </c>
       <c r="G74" t="n">
-        <v>0.123</v>
+        <v>0.1174</v>
       </c>
       <c r="H74" t="n">
-        <v>0.1174</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I74" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="J74" t="n">
         <v>0.19</v>
       </c>
-      <c r="K74" t="inlineStr">
+      <c r="J74" t="inlineStr">
         <is>
           <t>Lojistik / Depolama</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
-      <c r="P74" t="n">
+      <c r="K74" t="n">
         <v>61</v>
       </c>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
           <t>SAHOL</t>
         </is>
       </c>
+      <c r="B75" t="n">
+        <v>5</v>
+      </c>
       <c r="C75" t="n">
-        <v>5</v>
+        <v>0.87</v>
       </c>
       <c r="D75" t="n">
-        <v>0.87</v>
+        <v>0.0042</v>
       </c>
       <c r="E75" t="n">
-        <v>0.0042</v>
+        <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>0.0471</v>
       </c>
       <c r="G75" t="n">
-        <v>0.0471</v>
+        <v>0.095</v>
       </c>
       <c r="H75" t="n">
-        <v>0.095</v>
+        <v>0.03</v>
       </c>
       <c r="I75" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="J75" t="n">
         <v>0.14</v>
       </c>
-      <c r="K75" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t>Holding</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
-      <c r="O75" t="inlineStr"/>
-      <c r="P75" t="n">
+      <c r="K75" t="n">
         <v>38</v>
       </c>
-      <c r="Q75" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
           <t>SASA</t>
         </is>
       </c>
+      <c r="B76" t="n">
+        <v>5</v>
+      </c>
       <c r="C76" t="n">
-        <v>5</v>
+        <v>0.93</v>
       </c>
       <c r="D76" t="n">
-        <v>0.93</v>
+        <v>-0.0941</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.0941</v>
+        <v>0.08790000000000001</v>
       </c>
       <c r="F76" t="n">
-        <v>0.08790000000000001</v>
+        <v>-0.1842</v>
       </c>
       <c r="G76" t="n">
-        <v>-0.1842</v>
+        <v>-0.3946</v>
       </c>
       <c r="H76" t="n">
-        <v>-0.3946</v>
+        <v>0.08</v>
       </c>
       <c r="I76" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="J76" t="n">
         <v>0.39</v>
       </c>
-      <c r="K76" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t>Polyester / Kimya</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
-      <c r="P76" t="n">
+      <c r="K76" t="n">
         <v>23</v>
       </c>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
           <t>SISE</t>
         </is>
       </c>
+      <c r="B77" t="n">
+        <v>3</v>
+      </c>
       <c r="C77" t="n">
-        <v>3</v>
+        <v>4.05</v>
       </c>
       <c r="D77" t="n">
-        <v>4.05</v>
+        <v>0.0199</v>
       </c>
       <c r="E77" t="n">
-        <v>0.0199</v>
+        <v>0.2576</v>
       </c>
       <c r="F77" t="n">
-        <v>0.2576</v>
+        <v>0.0401</v>
       </c>
       <c r="G77" t="n">
-        <v>0.0401</v>
+        <v>0.0551</v>
       </c>
       <c r="H77" t="n">
-        <v>0.0551</v>
+        <v>0.11</v>
       </c>
       <c r="I77" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="J77" t="n">
         <v>0.32</v>
       </c>
-      <c r="K77" t="inlineStr">
+      <c r="J77" t="inlineStr">
         <is>
           <t>Cam Sanayi</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
-      <c r="P77" t="n">
+      <c r="K77" t="n">
         <v>45</v>
       </c>
-      <c r="Q77" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
           <t>SNGYO</t>
         </is>
       </c>
+      <c r="B78" t="n">
+        <v>5</v>
+      </c>
       <c r="C78" t="n">
-        <v>5</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="D78" t="n">
-        <v>8.630000000000001</v>
+        <v>-0.0013</v>
       </c>
       <c r="E78" t="n">
-        <v>-0.0013</v>
+        <v>0.6172</v>
       </c>
       <c r="F78" t="n">
-        <v>0.6172</v>
+        <v>-0.0022</v>
       </c>
       <c r="G78" t="n">
-        <v>-0.0022</v>
+        <v>-0.3257</v>
       </c>
       <c r="H78" t="n">
-        <v>-0.3257</v>
+        <v>0.02</v>
       </c>
       <c r="I78" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J78" t="n">
         <v>0.09</v>
       </c>
-      <c r="K78" t="inlineStr">
+      <c r="J78" t="inlineStr">
         <is>
           <t>Gayrimenkul Yatırım Ort.</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr"/>
-      <c r="P78" t="n">
+      <c r="K78" t="n">
         <v>38</v>
       </c>
-      <c r="Q78" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
           <t>SOKM</t>
         </is>
       </c>
+      <c r="B79" t="n">
+        <v>4</v>
+      </c>
       <c r="C79" t="n">
-        <v>4</v>
+        <v>2.61</v>
       </c>
       <c r="D79" t="n">
-        <v>2.61</v>
+        <v>-0.0255</v>
       </c>
       <c r="E79" t="n">
-        <v>-0.0255</v>
+        <v>0.1886</v>
       </c>
       <c r="F79" t="n">
-        <v>0.1886</v>
+        <v>-0.07920000000000001</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.07920000000000001</v>
+        <v>-0.0065</v>
       </c>
       <c r="H79" t="n">
-        <v>-0.0065</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I79" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="J79" t="n">
         <v>0.14</v>
       </c>
-      <c r="K79" t="inlineStr">
+      <c r="J79" t="inlineStr">
         <is>
           <t>Perakende Ticaret</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
-      <c r="P79" t="n">
+      <c r="K79" t="n">
         <v>33</v>
       </c>
-      <c r="Q79" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
           <t>TABGD</t>
         </is>
       </c>
+      <c r="B80" t="n">
+        <v>4</v>
+      </c>
       <c r="C80" t="n">
-        <v>4</v>
+        <v>5.72</v>
       </c>
       <c r="D80" t="n">
-        <v>5.72</v>
+        <v>0.077</v>
       </c>
       <c r="E80" t="n">
-        <v>0.077</v>
+        <v>0.1822</v>
       </c>
       <c r="F80" t="n">
-        <v>0.1822</v>
+        <v>0.1254</v>
       </c>
       <c r="G80" t="n">
-        <v>0.1254</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="H80" t="n">
-        <v>0.09320000000000001</v>
+        <v>0.37</v>
       </c>
       <c r="I80" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="J80" t="n">
         <v>0.17</v>
       </c>
-      <c r="K80" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t>Restoran / Gıda</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr"/>
-      <c r="P80" t="n">
+      <c r="K80" t="n">
         <v>57</v>
       </c>
-      <c r="Q80" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
           <t>TAVHL</t>
         </is>
       </c>
+      <c r="B81" t="n">
+        <v>8</v>
+      </c>
       <c r="C81" t="n">
-        <v>8</v>
+        <v>2.25</v>
       </c>
       <c r="D81" t="n">
-        <v>2.25</v>
+        <v>0.0276</v>
       </c>
       <c r="E81" t="n">
-        <v>0.0276</v>
+        <v>0.4023</v>
       </c>
       <c r="F81" t="n">
-        <v>0.4023</v>
+        <v>0.0859</v>
       </c>
       <c r="G81" t="n">
-        <v>0.0859</v>
+        <v>0.2785</v>
       </c>
       <c r="H81" t="n">
-        <v>0.2785</v>
+        <v>0.11</v>
       </c>
       <c r="I81" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="J81" t="n">
         <v>0.42</v>
       </c>
-      <c r="K81" t="inlineStr">
+      <c r="J81" t="inlineStr">
         <is>
           <t>Havalimanı Hizmetleri</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr"/>
-      <c r="P81" t="n">
+      <c r="K81" t="n">
         <v>32</v>
       </c>
-      <c r="Q81" t="inlineStr">
+      <c r="L81" t="inlineStr">
         <is>
           <t>⚠️ Dikkat (%6.3)</t>
         </is>
       </c>
-      <c r="R81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
           <t>TCELL</t>
         </is>
       </c>
+      <c r="B82" t="n">
+        <v>4</v>
+      </c>
       <c r="C82" t="n">
-        <v>4</v>
+        <v>3.37</v>
       </c>
       <c r="D82" t="n">
-        <v>3.37</v>
+        <v>0.0315</v>
       </c>
       <c r="E82" t="n">
-        <v>0.0315</v>
+        <v>0.2536</v>
       </c>
       <c r="F82" t="n">
-        <v>0.2536</v>
+        <v>0.0672</v>
       </c>
       <c r="G82" t="n">
-        <v>0.0672</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="H82" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="I82" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="J82" t="n">
         <v>0.32</v>
       </c>
-      <c r="K82" t="inlineStr">
+      <c r="J82" t="inlineStr">
         <is>
           <t>Telekomünikasyon</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr"/>
-      <c r="P82" t="n">
+      <c r="K82" t="n">
         <v>26</v>
       </c>
-      <c r="Q82" t="inlineStr">
+      <c r="L82" t="inlineStr">
         <is>
           <t>⚠️ Dikkat (%6.3)</t>
         </is>
       </c>
-      <c r="R82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
           <t>TCKRC</t>
         </is>
       </c>
+      <c r="B83" t="n">
+        <v>7</v>
+      </c>
       <c r="C83" t="n">
-        <v>7</v>
+        <v>12.15</v>
       </c>
       <c r="D83" t="n">
-        <v>12.15</v>
+        <v>0.1974</v>
       </c>
       <c r="E83" t="n">
-        <v>0.1974</v>
+        <v>0.4043</v>
       </c>
       <c r="F83" t="n">
-        <v>0.4043</v>
+        <v>0.26</v>
       </c>
       <c r="G83" t="n">
-        <v>0.26</v>
+        <v>0.3346</v>
       </c>
       <c r="H83" t="n">
-        <v>0.3346</v>
+        <v>0.22</v>
       </c>
       <c r="I83" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="J83" t="n">
         <v>0.12</v>
       </c>
-      <c r="K83" t="inlineStr">
+      <c r="J83" t="inlineStr">
         <is>
           <t>Dayanıklı Tüketim</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
-      <c r="O83" t="inlineStr"/>
-      <c r="P83" t="n">
+      <c r="K83" t="n">
         <v>55</v>
       </c>
-      <c r="Q83" t="inlineStr">
+      <c r="L83" t="inlineStr">
         <is>
           <t>🚨 RİSKLİ (%50.1)</t>
         </is>
       </c>
-      <c r="R83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
           <t>THYAO</t>
         </is>
       </c>
+      <c r="B84" t="n">
+        <v>4</v>
+      </c>
       <c r="C84" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="D84" t="n">
-        <v>2.4</v>
+        <v>0.053</v>
       </c>
       <c r="E84" t="n">
-        <v>0.053</v>
+        <v>0.0636</v>
       </c>
       <c r="F84" t="n">
-        <v>0.0636</v>
+        <v>0.1225</v>
       </c>
       <c r="G84" t="n">
-        <v>0.1225</v>
+        <v>0.0275</v>
       </c>
       <c r="H84" t="n">
-        <v>0.0275</v>
+        <v>0.14</v>
       </c>
       <c r="I84" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="J84" t="n">
         <v>0.39</v>
       </c>
-      <c r="K84" t="inlineStr">
+      <c r="J84" t="inlineStr">
         <is>
           <t>Ulaştırma / Havacılık</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
-      <c r="P84" t="n">
+      <c r="K84" t="n">
         <v>46</v>
       </c>
-      <c r="Q84" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
           <t>TKFEN</t>
         </is>
       </c>
+      <c r="B85" t="n">
+        <v>5</v>
+      </c>
       <c r="C85" t="n">
-        <v>5</v>
+        <v>3.35</v>
       </c>
       <c r="D85" t="n">
-        <v>3.35</v>
+        <v>-0.0351</v>
       </c>
       <c r="E85" t="n">
-        <v>-0.0351</v>
+        <v>0.165</v>
       </c>
       <c r="F85" t="n">
-        <v>0.165</v>
+        <v>-0.0718</v>
       </c>
       <c r="G85" t="n">
-        <v>-0.0718</v>
+        <v>0.0756</v>
       </c>
       <c r="H85" t="n">
-        <v>0.0756</v>
+        <v>0.16</v>
       </c>
       <c r="I85" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="J85" t="n">
         <v>0.19</v>
       </c>
-      <c r="K85" t="inlineStr">
+      <c r="J85" t="inlineStr">
         <is>
           <t>İnşaat / Taahhüt / Tarım</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr"/>
-      <c r="P85" t="n">
+      <c r="K85" t="n">
         <v>44</v>
       </c>
-      <c r="Q85" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
           <t>TOASO</t>
         </is>
       </c>
+      <c r="B86" t="n">
+        <v>3</v>
+      </c>
       <c r="C86" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="D86" t="n">
-        <v>3.1</v>
+        <v>0.0589</v>
       </c>
       <c r="E86" t="n">
-        <v>0.0589</v>
+        <v>0.063</v>
       </c>
       <c r="F86" t="n">
-        <v>0.063</v>
+        <v>0.1934</v>
       </c>
       <c r="G86" t="n">
-        <v>0.1934</v>
+        <v>0.0293</v>
       </c>
       <c r="H86" t="n">
-        <v>0.0293</v>
+        <v>0.49</v>
       </c>
       <c r="I86" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="J86" t="n">
         <v>0.33</v>
       </c>
-      <c r="K86" t="inlineStr">
+      <c r="J86" t="inlineStr">
         <is>
           <t>Otomotiv Üretim</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
-      <c r="O86" t="inlineStr"/>
-      <c r="P86" t="n">
+      <c r="K86" t="n">
         <v>33</v>
       </c>
-      <c r="Q86" t="inlineStr">
+      <c r="L86" t="inlineStr">
         <is>
           <t>🚨 RİSKLİ (%24.0)</t>
         </is>
       </c>
-      <c r="R86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
           <t>TRALT</t>
         </is>
       </c>
+      <c r="B87" t="n">
+        <v>3</v>
+      </c>
       <c r="C87" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D87" t="n">
-        <v>15</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="E87" t="n">
-        <v>0.08169999999999999</v>
+        <v>0.6573</v>
       </c>
       <c r="F87" t="n">
-        <v>0.6573</v>
+        <v>0.0945</v>
       </c>
       <c r="G87" t="n">
-        <v>0.0945</v>
+        <v>0.2433</v>
       </c>
       <c r="H87" t="n">
-        <v>0.2433</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I87" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="J87" t="n">
-        <v>0</v>
-      </c>
-      <c r="K87" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J87" t="inlineStr">
         <is>
           <t>Madencilik / Altın</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr"/>
-      <c r="P87" t="n">
+      <c r="K87" t="n">
         <v>59</v>
       </c>
-      <c r="Q87" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
           <t>TRENJ</t>
         </is>
       </c>
+      <c r="B88" t="n">
+        <v>4</v>
+      </c>
       <c r="C88" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D88" t="n">
-        <v>15</v>
+        <v>0.0254</v>
       </c>
       <c r="E88" t="n">
-        <v>0.0254</v>
+        <v>0.6276</v>
       </c>
       <c r="F88" t="n">
-        <v>0.6276</v>
+        <v>0.1046</v>
       </c>
       <c r="G88" t="n">
-        <v>0.1046</v>
+        <v>0.1948</v>
       </c>
       <c r="H88" t="n">
-        <v>0.1948</v>
+        <v>0.08</v>
       </c>
       <c r="I88" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="J88" t="n">
-        <v>0</v>
-      </c>
-      <c r="K88" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J88" t="inlineStr">
         <is>
           <t>Enerji / Sanayi</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
-      <c r="O88" t="inlineStr"/>
-      <c r="P88" t="n">
+      <c r="K88" t="n">
         <v>55</v>
       </c>
-      <c r="Q88" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R88" t="inlineStr"/>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
           <t>TRGYO</t>
         </is>
       </c>
+      <c r="B89" t="n">
+        <v>5</v>
+      </c>
       <c r="C89" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D89" t="n">
-        <v>15</v>
+        <v>0.0454</v>
       </c>
       <c r="E89" t="n">
-        <v>0.0454</v>
+        <v>0.7359</v>
       </c>
       <c r="F89" t="n">
-        <v>0.7359</v>
+        <v>0.0583</v>
       </c>
       <c r="G89" t="n">
-        <v>0.0583</v>
+        <v>0.8191000000000001</v>
       </c>
       <c r="H89" t="n">
-        <v>0.8191000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="I89" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="J89" t="n">
         <v>0.06</v>
       </c>
-      <c r="K89" t="inlineStr">
+      <c r="J89" t="inlineStr">
         <is>
           <t>Gayrimenkul Yatırım Ort.</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr"/>
-      <c r="P89" t="n">
+      <c r="K89" t="n">
         <v>57</v>
       </c>
-      <c r="Q89" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
           <t>TRMET</t>
         </is>
       </c>
+      <c r="B90" t="n">
+        <v>3</v>
+      </c>
       <c r="C90" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D90" t="n">
-        <v>15</v>
+        <v>0.0319</v>
       </c>
       <c r="E90" t="n">
-        <v>0.0319</v>
+        <v>0.6296</v>
       </c>
       <c r="F90" t="n">
-        <v>0.6296</v>
+        <v>0.0696</v>
       </c>
       <c r="G90" t="n">
-        <v>0.0696</v>
+        <v>0.1134</v>
       </c>
       <c r="H90" t="n">
-        <v>0.1134</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I90" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="J90" t="n">
-        <v>0</v>
-      </c>
-      <c r="K90" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J90" t="inlineStr">
         <is>
           <t>Metal / Maden</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
-      <c r="O90" t="inlineStr"/>
-      <c r="P90" t="n">
+      <c r="K90" t="n">
         <v>49</v>
       </c>
-      <c r="Q90" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R90" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
+          <t>TSKB</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>TSKB</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -5366,19 +4446,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D91" t="n">
+        <v>0.0323</v>
       </c>
       <c r="E91" t="n">
-        <v>0.0323</v>
+        <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>0</v>
+        <v>0.2366</v>
       </c>
       <c r="G91" t="n">
-        <v>0.2366</v>
+        <v>0</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -5386,253 +4464,205 @@
       <c r="I91" t="n">
         <v>0</v>
       </c>
-      <c r="J91" t="n">
-        <v>0</v>
-      </c>
-      <c r="K91" t="inlineStr">
+      <c r="J91" t="inlineStr">
         <is>
           <t>Bankacılık</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
-      <c r="O91" t="inlineStr"/>
-      <c r="P91" t="n">
+      <c r="K91" t="n">
         <v>70</v>
       </c>
-      <c r="Q91" t="inlineStr">
+      <c r="L91" t="inlineStr">
         <is>
           <t>✅ Finans / Muaf</t>
         </is>
       </c>
-      <c r="R91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
           <t>TTKOM</t>
         </is>
       </c>
+      <c r="B92" t="n">
+        <v>4</v>
+      </c>
       <c r="C92" t="n">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="D92" t="n">
-        <v>2.75</v>
+        <v>0.0382</v>
       </c>
       <c r="E92" t="n">
-        <v>0.0382</v>
+        <v>0.3932</v>
       </c>
       <c r="F92" t="n">
-        <v>0.3932</v>
+        <v>0.0924</v>
       </c>
       <c r="G92" t="n">
-        <v>0.0924</v>
+        <v>0.0819</v>
       </c>
       <c r="H92" t="n">
-        <v>0.0819</v>
+        <v>0.11</v>
       </c>
       <c r="I92" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="J92" t="n">
         <v>0.23</v>
       </c>
-      <c r="K92" t="inlineStr">
+      <c r="J92" t="inlineStr">
         <is>
           <t>Telekomünikasyon</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
-      <c r="O92" t="inlineStr"/>
-      <c r="P92" t="n">
+      <c r="K92" t="n">
         <v>19</v>
       </c>
-      <c r="Q92" t="inlineStr">
+      <c r="L92" t="inlineStr">
         <is>
           <t>⚠️ Dikkat (%9.0)</t>
         </is>
       </c>
-      <c r="R92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
           <t>TTRAK</t>
         </is>
       </c>
+      <c r="B93" t="n">
+        <v>6</v>
+      </c>
       <c r="C93" t="n">
-        <v>6</v>
+        <v>2.66</v>
       </c>
       <c r="D93" t="n">
-        <v>2.66</v>
+        <v>-0.014</v>
       </c>
       <c r="E93" t="n">
-        <v>-0.014</v>
+        <v>0.0901</v>
       </c>
       <c r="F93" t="n">
-        <v>0.0901</v>
+        <v>-0.0313</v>
       </c>
       <c r="G93" t="n">
-        <v>-0.0313</v>
+        <v>0.0539</v>
       </c>
       <c r="H93" t="n">
-        <v>0.0539</v>
+        <v>0.31</v>
       </c>
       <c r="I93" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="J93" t="n">
         <v>0.34</v>
       </c>
-      <c r="K93" t="inlineStr">
+      <c r="J93" t="inlineStr">
         <is>
           <t>Traktör / İş Makineleri</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
-      <c r="O93" t="inlineStr"/>
-      <c r="P93" t="n">
+      <c r="K93" t="n">
         <v>35</v>
       </c>
-      <c r="Q93" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R93" t="inlineStr"/>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
           <t>TUKAS</t>
         </is>
       </c>
+      <c r="B94" t="n">
+        <v>5</v>
+      </c>
       <c r="C94" t="n">
-        <v>5</v>
+        <v>4.57</v>
       </c>
       <c r="D94" t="n">
-        <v>4.57</v>
+        <v>-0.049</v>
       </c>
       <c r="E94" t="n">
-        <v>-0.049</v>
+        <v>0.146</v>
       </c>
       <c r="F94" t="n">
-        <v>0.146</v>
+        <v>-0.0725</v>
       </c>
       <c r="G94" t="n">
-        <v>-0.0725</v>
+        <v>-0.2213</v>
       </c>
       <c r="H94" t="n">
-        <v>-0.2213</v>
+        <v>0.09</v>
       </c>
       <c r="I94" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="J94" t="n">
         <v>0.24</v>
       </c>
-      <c r="K94" t="inlineStr">
+      <c r="J94" t="inlineStr">
         <is>
           <t>Gıda İmalatı</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
-      <c r="O94" t="inlineStr"/>
-      <c r="P94" t="n">
+      <c r="K94" t="n">
         <v>38</v>
       </c>
-      <c r="Q94" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
           <t>TUPRS</t>
         </is>
       </c>
+      <c r="B95" t="n">
+        <v>9</v>
+      </c>
       <c r="C95" t="n">
-        <v>9</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="D95" t="n">
-        <v>9.539999999999999</v>
+        <v>0.0808</v>
       </c>
       <c r="E95" t="n">
-        <v>0.0808</v>
+        <v>0.158</v>
       </c>
       <c r="F95" t="n">
-        <v>0.158</v>
+        <v>0.1523</v>
       </c>
       <c r="G95" t="n">
-        <v>0.1523</v>
+        <v>0.1187</v>
       </c>
       <c r="H95" t="n">
-        <v>0.1187</v>
+        <v>0.45</v>
       </c>
       <c r="I95" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="J95" t="n">
         <v>0.08</v>
       </c>
-      <c r="K95" t="inlineStr">
+      <c r="J95" t="inlineStr">
         <is>
           <t>Petrol Rafineri</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
-      <c r="O95" t="inlineStr"/>
-      <c r="P95" t="n">
+      <c r="K95" t="n">
         <v>75</v>
       </c>
-      <c r="Q95" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
+          <t>TURSG</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>TURSG</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -5640,19 +4670,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D96" t="n">
+        <v>0.117</v>
       </c>
       <c r="E96" t="n">
-        <v>0.117</v>
+        <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>0</v>
+        <v>0.4997</v>
       </c>
       <c r="G96" t="n">
-        <v>0.4997</v>
+        <v>0</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -5660,91 +4688,73 @@
       <c r="I96" t="n">
         <v>0</v>
       </c>
-      <c r="J96" t="n">
-        <v>0</v>
-      </c>
-      <c r="K96" t="inlineStr">
+      <c r="J96" t="inlineStr">
         <is>
           <t>Sigorta</t>
         </is>
       </c>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
-      <c r="O96" t="inlineStr"/>
-      <c r="P96" t="n">
+      <c r="K96" t="n">
         <v>100</v>
       </c>
-      <c r="Q96" t="inlineStr">
+      <c r="L96" t="inlineStr">
         <is>
           <t>✅ Finans / Muaf</t>
         </is>
       </c>
-      <c r="R96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
           <t>ULKER</t>
         </is>
       </c>
+      <c r="B97" t="n">
+        <v>6</v>
+      </c>
       <c r="C97" t="n">
-        <v>6</v>
+        <v>4.25</v>
       </c>
       <c r="D97" t="n">
-        <v>4.25</v>
+        <v>0.03</v>
       </c>
       <c r="E97" t="n">
-        <v>0.03</v>
+        <v>0.2456</v>
       </c>
       <c r="F97" t="n">
-        <v>0.2456</v>
+        <v>0.0847</v>
       </c>
       <c r="G97" t="n">
-        <v>0.0847</v>
+        <v>0.0514</v>
       </c>
       <c r="H97" t="n">
-        <v>0.0514</v>
+        <v>0.19</v>
       </c>
       <c r="I97" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="J97" t="n">
         <v>0.45</v>
       </c>
-      <c r="K97" t="inlineStr">
+      <c r="J97" t="inlineStr">
         <is>
           <t>Gıda / Atıştırmalık</t>
         </is>
       </c>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
-      <c r="O97" t="inlineStr"/>
-      <c r="P97" t="n">
+      <c r="K97" t="n">
         <v>51</v>
       </c>
-      <c r="Q97" t="inlineStr">
-        <is>
-          <t>✅ Temiz</t>
-        </is>
-      </c>
-      <c r="R97" t="inlineStr"/>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>✅ Temiz</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
+          <t>VAKBN</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>VAKBN</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -5752,19 +4762,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D98" t="n">
+        <v>0.0152</v>
       </c>
       <c r="E98" t="n">
-        <v>0.0152</v>
+        <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>0</v>
+        <v>0.2475</v>
       </c>
       <c r="G98" t="n">
-        <v>0.2475</v>
+        <v>0</v>
       </c>
       <c r="H98" t="n">
         <v>0</v>
@@ -5772,91 +4780,73 @@
       <c r="I98" t="n">
         <v>0</v>
       </c>
-      <c r="J98" t="n">
-        <v>0</v>
-      </c>
-      <c r="K98" t="inlineStr">
+      <c r="J98" t="inlineStr">
         <is>
           <t>Bankacılık</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
-      <c r="O98" t="inlineStr"/>
-      <c r="P98" t="n">
+      <c r="K98" t="n">
         <v>40</v>
       </c>
-      <c r="Q98" t="inlineStr">
+      <c r="L98" t="inlineStr">
         <is>
           <t>✅ Finans / Muaf</t>
         </is>
       </c>
-      <c r="R98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
           <t>VESTL</t>
         </is>
       </c>
+      <c r="B99" t="n">
+        <v>3</v>
+      </c>
       <c r="C99" t="n">
-        <v>3</v>
+        <v>-2.85</v>
       </c>
       <c r="D99" t="n">
-        <v>-2.85</v>
+        <v>-0.1259</v>
       </c>
       <c r="E99" t="n">
-        <v>-0.1259</v>
+        <v>0.1379</v>
       </c>
       <c r="F99" t="n">
-        <v>0.1379</v>
+        <v>-1.1709</v>
       </c>
       <c r="G99" t="n">
-        <v>-1.1709</v>
+        <v>-0.2748</v>
       </c>
       <c r="H99" t="n">
-        <v>-0.2748</v>
+        <v>0.12</v>
       </c>
       <c r="I99" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="J99" t="n">
         <v>0.53</v>
       </c>
-      <c r="K99" t="inlineStr">
+      <c r="J99" t="inlineStr">
         <is>
           <t>Dayanıklı Tüketim / Elektronik</t>
         </is>
       </c>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
-      <c r="O99" t="inlineStr"/>
-      <c r="P99" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q99" t="inlineStr">
+      <c r="K99" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" t="inlineStr">
         <is>
           <t>⚠️ Dikkat (%6.1)</t>
         </is>
       </c>
-      <c r="R99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
+          <t>YKBNK</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>YKBNK</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -5864,19 +4854,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D100" t="n">
+        <v>0.0158</v>
       </c>
       <c r="E100" t="n">
-        <v>0.0158</v>
+        <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>0</v>
+        <v>0.2178</v>
       </c>
       <c r="G100" t="n">
-        <v>0.2178</v>
+        <v>0</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
@@ -5884,81 +4872,63 @@
       <c r="I100" t="n">
         <v>0</v>
       </c>
-      <c r="J100" t="n">
-        <v>0</v>
-      </c>
-      <c r="K100" t="inlineStr">
+      <c r="J100" t="inlineStr">
         <is>
           <t>Bankacılık</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
-      <c r="O100" t="inlineStr"/>
-      <c r="P100" t="n">
+      <c r="K100" t="n">
         <v>40</v>
       </c>
-      <c r="Q100" t="inlineStr">
+      <c r="L100" t="inlineStr">
         <is>
           <t>✅ Finans / Muaf</t>
         </is>
       </c>
-      <c r="R100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>26.10.2026</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
           <t>ZOREN</t>
         </is>
       </c>
+      <c r="B101" t="n">
+        <v>4</v>
+      </c>
       <c r="C101" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D101" t="n">
+        <v>-0.0809</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="F101" t="n">
+        <v>-0.182</v>
+      </c>
+      <c r="G101" t="n">
+        <v>-0.4132</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Elektrik / Enerji</t>
+        </is>
+      </c>
+      <c r="K101" t="n">
         <v>4</v>
       </c>
-      <c r="D101" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="E101" t="n">
-        <v>-0.0809</v>
-      </c>
-      <c r="F101" t="n">
-        <v>0.079</v>
-      </c>
-      <c r="G101" t="n">
-        <v>-0.182</v>
-      </c>
-      <c r="H101" t="n">
-        <v>-0.4132</v>
-      </c>
-      <c r="I101" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J101" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>Elektrik / Enerji</t>
-        </is>
-      </c>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
-      <c r="O101" t="inlineStr"/>
-      <c r="P101" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q101" t="inlineStr">
+      <c r="L101" t="inlineStr">
         <is>
           <t>⚠️ Dikkat (%10.6)</t>
         </is>
       </c>
-      <c r="R101" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
